--- a/03_Analysis/analysis.xlsx
+++ b/03_Analysis/analysis.xlsx
@@ -19,6 +19,15 @@
     <sheet name="SubCategory" sheetId="10" state="visible" r:id="rId10"/>
     <sheet name="Customers" sheetId="11" state="visible" r:id="rId11"/>
     <sheet name="Segments" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Cohort_Retention_Pct" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Cohort_Revenue" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="Cohort_Year_Summary" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="New_vs_Returning" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="Discount_Bands" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="Discount_SubCategory" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="Discount_Category" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="Discount_Region" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="Product_Quadrants" sheetId="21" state="visible" r:id="rId21"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -24210,6 +24219,6364 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AW43"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>cohort</t>
+        </is>
+      </c>
+      <c r="B1" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F1" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1" t="n">
+        <v>5</v>
+      </c>
+      <c r="H1" t="n">
+        <v>6</v>
+      </c>
+      <c r="I1" t="n">
+        <v>7</v>
+      </c>
+      <c r="J1" t="n">
+        <v>8</v>
+      </c>
+      <c r="K1" t="n">
+        <v>9</v>
+      </c>
+      <c r="L1" t="n">
+        <v>10</v>
+      </c>
+      <c r="M1" t="n">
+        <v>11</v>
+      </c>
+      <c r="N1" t="n">
+        <v>12</v>
+      </c>
+      <c r="O1" t="n">
+        <v>13</v>
+      </c>
+      <c r="P1" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q1" t="n">
+        <v>15</v>
+      </c>
+      <c r="R1" t="n">
+        <v>16</v>
+      </c>
+      <c r="S1" t="n">
+        <v>17</v>
+      </c>
+      <c r="T1" t="n">
+        <v>18</v>
+      </c>
+      <c r="U1" t="n">
+        <v>19</v>
+      </c>
+      <c r="V1" t="n">
+        <v>20</v>
+      </c>
+      <c r="W1" t="n">
+        <v>21</v>
+      </c>
+      <c r="X1" t="n">
+        <v>22</v>
+      </c>
+      <c r="Y1" t="n">
+        <v>23</v>
+      </c>
+      <c r="Z1" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA1" t="n">
+        <v>25</v>
+      </c>
+      <c r="AB1" t="n">
+        <v>26</v>
+      </c>
+      <c r="AC1" t="n">
+        <v>27</v>
+      </c>
+      <c r="AD1" t="n">
+        <v>28</v>
+      </c>
+      <c r="AE1" t="n">
+        <v>29</v>
+      </c>
+      <c r="AF1" t="n">
+        <v>30</v>
+      </c>
+      <c r="AG1" t="n">
+        <v>31</v>
+      </c>
+      <c r="AH1" t="n">
+        <v>32</v>
+      </c>
+      <c r="AI1" t="n">
+        <v>33</v>
+      </c>
+      <c r="AJ1" t="n">
+        <v>34</v>
+      </c>
+      <c r="AK1" t="n">
+        <v>35</v>
+      </c>
+      <c r="AL1" t="n">
+        <v>36</v>
+      </c>
+      <c r="AM1" t="n">
+        <v>37</v>
+      </c>
+      <c r="AN1" t="n">
+        <v>38</v>
+      </c>
+      <c r="AO1" t="n">
+        <v>39</v>
+      </c>
+      <c r="AP1" t="n">
+        <v>40</v>
+      </c>
+      <c r="AQ1" t="n">
+        <v>41</v>
+      </c>
+      <c r="AR1" t="n">
+        <v>42</v>
+      </c>
+      <c r="AS1" t="n">
+        <v>43</v>
+      </c>
+      <c r="AT1" t="n">
+        <v>44</v>
+      </c>
+      <c r="AU1" t="n">
+        <v>45</v>
+      </c>
+      <c r="AV1" t="n">
+        <v>46</v>
+      </c>
+      <c r="AW1" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2014-01</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>100</v>
+      </c>
+      <c r="C2" t="n">
+        <v>9.375</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="F2" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="I2" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="J2" t="n">
+        <v>15.625</v>
+      </c>
+      <c r="K2" t="n">
+        <v>9.375</v>
+      </c>
+      <c r="L2" t="n">
+        <v>21.875</v>
+      </c>
+      <c r="M2" t="n">
+        <v>15.625</v>
+      </c>
+      <c r="N2" t="n">
+        <v>9.375</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
+        <v>9.375</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>9.375</v>
+      </c>
+      <c r="R2" t="n">
+        <v>9.375</v>
+      </c>
+      <c r="S2" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="T2" t="n">
+        <v>9.375</v>
+      </c>
+      <c r="U2" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="V2" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" t="n">
+        <v>18.75</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>15.625</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>3.125</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>15.625</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>9.375</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>15.625</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>3.125</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>3.125</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>34.375</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>28.125</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>18.75</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>15.625</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>3.125</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>18.75</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>15.625</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>3.125</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>28.125</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>28.125</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>31.25</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>18.75</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2014-02</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>100</v>
+      </c>
+      <c r="C3" t="n">
+        <v>16.66666666666666</v>
+      </c>
+      <c r="D3" t="n">
+        <v>8.333333333333332</v>
+      </c>
+      <c r="E3" t="n">
+        <v>4.166666666666666</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>8.333333333333332</v>
+      </c>
+      <c r="H3" t="n">
+        <v>8.333333333333332</v>
+      </c>
+      <c r="I3" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="J3" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="K3" t="n">
+        <v>16.66666666666666</v>
+      </c>
+      <c r="L3" t="n">
+        <v>16.66666666666666</v>
+      </c>
+      <c r="M3" t="n">
+        <v>4.166666666666666</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>8.333333333333332</v>
+      </c>
+      <c r="P3" t="n">
+        <v>8.333333333333332</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>8.333333333333332</v>
+      </c>
+      <c r="R3" t="n">
+        <v>8.333333333333332</v>
+      </c>
+      <c r="S3" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" t="n">
+        <v>25</v>
+      </c>
+      <c r="V3" t="n">
+        <v>8.333333333333332</v>
+      </c>
+      <c r="W3" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="X3" t="n">
+        <v>8.333333333333332</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>4.166666666666666</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>4.166666666666666</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>16.66666666666666</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>16.66666666666666</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>16.66666666666666</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>16.66666666666666</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>16.66666666666666</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>16.66666666666666</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>16.66666666666666</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>16.66666666666666</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>8.333333333333332</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>8.333333333333332</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>20.83333333333334</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>16.66666666666666</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>25</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>25</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AW3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2014-03</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>100</v>
+      </c>
+      <c r="C4" t="n">
+        <v>6.153846153846154</v>
+      </c>
+      <c r="D4" t="n">
+        <v>3.076923076923077</v>
+      </c>
+      <c r="E4" t="n">
+        <v>12.30769230769231</v>
+      </c>
+      <c r="F4" t="n">
+        <v>10.76923076923077</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>10.76923076923077</v>
+      </c>
+      <c r="I4" t="n">
+        <v>7.692307692307693</v>
+      </c>
+      <c r="J4" t="n">
+        <v>12.30769230769231</v>
+      </c>
+      <c r="K4" t="n">
+        <v>9.230769230769232</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1.538461538461539</v>
+      </c>
+      <c r="M4" t="n">
+        <v>3.076923076923077</v>
+      </c>
+      <c r="N4" t="n">
+        <v>9.230769230769232</v>
+      </c>
+      <c r="O4" t="n">
+        <v>4.615384615384616</v>
+      </c>
+      <c r="P4" t="n">
+        <v>7.692307692307693</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>7.692307692307693</v>
+      </c>
+      <c r="R4" t="n">
+        <v>4.615384615384616</v>
+      </c>
+      <c r="S4" t="n">
+        <v>7.692307692307693</v>
+      </c>
+      <c r="T4" t="n">
+        <v>13.84615384615385</v>
+      </c>
+      <c r="U4" t="n">
+        <v>16.92307692307692</v>
+      </c>
+      <c r="V4" t="n">
+        <v>20</v>
+      </c>
+      <c r="W4" t="n">
+        <v>18.46153846153846</v>
+      </c>
+      <c r="X4" t="n">
+        <v>6.153846153846154</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>6.153846153846154</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>9.230769230769232</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>12.30769230769231</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>12.30769230769231</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>9.230769230769232</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>13.84615384615385</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>7.692307692307693</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>20</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>12.30769230769231</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>20</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>15.38461538461539</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>3.076923076923077</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>9.230769230769232</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>9.230769230769232</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>18.46153846153846</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>20</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>15.38461538461539</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>18.46153846153846</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>9.230769230769232</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>29.23076923076923</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>12.30769230769231</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>27.69230769230769</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>24.61538461538462</v>
+      </c>
+      <c r="AV4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2014-04</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>100</v>
+      </c>
+      <c r="C5" t="n">
+        <v>10.71428571428571</v>
+      </c>
+      <c r="D5" t="n">
+        <v>3.571428571428571</v>
+      </c>
+      <c r="E5" t="n">
+        <v>7.142857142857142</v>
+      </c>
+      <c r="F5" t="n">
+        <v>5.357142857142857</v>
+      </c>
+      <c r="G5" t="n">
+        <v>14.28571428571428</v>
+      </c>
+      <c r="H5" t="n">
+        <v>10.71428571428571</v>
+      </c>
+      <c r="I5" t="n">
+        <v>16.07142857142857</v>
+      </c>
+      <c r="J5" t="n">
+        <v>14.28571428571428</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1.785714285714286</v>
+      </c>
+      <c r="L5" t="n">
+        <v>7.142857142857142</v>
+      </c>
+      <c r="M5" t="n">
+        <v>8.928571428571429</v>
+      </c>
+      <c r="N5" t="n">
+        <v>14.28571428571428</v>
+      </c>
+      <c r="O5" t="n">
+        <v>17.85714285714286</v>
+      </c>
+      <c r="P5" t="n">
+        <v>10.71428571428571</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>8.928571428571429</v>
+      </c>
+      <c r="R5" t="n">
+        <v>10.71428571428571</v>
+      </c>
+      <c r="S5" t="n">
+        <v>16.07142857142857</v>
+      </c>
+      <c r="T5" t="n">
+        <v>5.357142857142857</v>
+      </c>
+      <c r="U5" t="n">
+        <v>25</v>
+      </c>
+      <c r="V5" t="n">
+        <v>19.64285714285714</v>
+      </c>
+      <c r="W5" t="n">
+        <v>5.357142857142857</v>
+      </c>
+      <c r="X5" t="n">
+        <v>3.571428571428571</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>8.928571428571429</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>14.28571428571428</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>16.07142857142857</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>14.28571428571428</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>8.928571428571429</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>25</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>10.71428571428571</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>25</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>26.78571428571428</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>7.142857142857142</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>5.357142857142857</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>25</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>5.357142857142857</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>19.64285714285714</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>8.928571428571429</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>14.28571428571428</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>26.78571428571428</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>14.28571428571428</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>25</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>25</v>
+      </c>
+      <c r="AU5" t="inlineStr"/>
+      <c r="AV5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2014-05</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>100</v>
+      </c>
+      <c r="C6" t="n">
+        <v>8.928571428571429</v>
+      </c>
+      <c r="D6" t="n">
+        <v>8.928571428571429</v>
+      </c>
+      <c r="E6" t="n">
+        <v>7.142857142857142</v>
+      </c>
+      <c r="F6" t="n">
+        <v>17.85714285714286</v>
+      </c>
+      <c r="G6" t="n">
+        <v>3.571428571428571</v>
+      </c>
+      <c r="H6" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="I6" t="n">
+        <v>17.85714285714286</v>
+      </c>
+      <c r="J6" t="n">
+        <v>7.142857142857142</v>
+      </c>
+      <c r="K6" t="n">
+        <v>5.357142857142857</v>
+      </c>
+      <c r="L6" t="n">
+        <v>7.142857142857142</v>
+      </c>
+      <c r="M6" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="N6" t="n">
+        <v>3.571428571428571</v>
+      </c>
+      <c r="O6" t="n">
+        <v>8.928571428571429</v>
+      </c>
+      <c r="P6" t="n">
+        <v>3.571428571428571</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>8.928571428571429</v>
+      </c>
+      <c r="R6" t="n">
+        <v>14.28571428571428</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10.71428571428571</v>
+      </c>
+      <c r="T6" t="n">
+        <v>19.64285714285714</v>
+      </c>
+      <c r="U6" t="n">
+        <v>14.28571428571428</v>
+      </c>
+      <c r="V6" t="n">
+        <v>8.928571428571429</v>
+      </c>
+      <c r="W6" t="n">
+        <v>3.571428571428571</v>
+      </c>
+      <c r="X6" t="n">
+        <v>5.357142857142857</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>8.928571428571429</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>8.928571428571429</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>7.142857142857142</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>19.64285714285714</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>14.28571428571428</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>23.21428571428572</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>23.21428571428572</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>7.142857142857142</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>5.357142857142857</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>5.357142857142857</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>8.928571428571429</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>7.142857142857142</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>19.64285714285714</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>10.71428571428571</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>30.35714285714285</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>16.07142857142857</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AU6" t="inlineStr"/>
+      <c r="AV6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2014-06</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>100</v>
+      </c>
+      <c r="C7" t="n">
+        <v>2.083333333333333</v>
+      </c>
+      <c r="D7" t="n">
+        <v>4.166666666666666</v>
+      </c>
+      <c r="E7" t="n">
+        <v>8.333333333333332</v>
+      </c>
+      <c r="F7" t="n">
+        <v>4.166666666666666</v>
+      </c>
+      <c r="G7" t="n">
+        <v>18.75</v>
+      </c>
+      <c r="H7" t="n">
+        <v>16.66666666666666</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.083333333333333</v>
+      </c>
+      <c r="J7" t="n">
+        <v>8.333333333333332</v>
+      </c>
+      <c r="K7" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="L7" t="n">
+        <v>10.41666666666667</v>
+      </c>
+      <c r="M7" t="n">
+        <v>10.41666666666667</v>
+      </c>
+      <c r="N7" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="O7" t="n">
+        <v>8.333333333333332</v>
+      </c>
+      <c r="P7" t="n">
+        <v>14.58333333333333</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>10.41666666666667</v>
+      </c>
+      <c r="R7" t="n">
+        <v>14.58333333333333</v>
+      </c>
+      <c r="S7" t="n">
+        <v>33.33333333333333</v>
+      </c>
+      <c r="T7" t="n">
+        <v>18.75</v>
+      </c>
+      <c r="U7" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="V7" t="n">
+        <v>4.166666666666666</v>
+      </c>
+      <c r="W7" t="n">
+        <v>18.75</v>
+      </c>
+      <c r="X7" t="n">
+        <v>10.41666666666667</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>8.333333333333332</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>10.41666666666667</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>8.333333333333332</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>4.166666666666666</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>22.91666666666666</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>20.83333333333334</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>14.58333333333333</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>29.16666666666667</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>8.333333333333332</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>18.75</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>18.75</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>10.41666666666667</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>27.08333333333333</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>14.58333333333333</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>29.16666666666667</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>22.91666666666666</v>
+      </c>
+      <c r="AS7" t="inlineStr"/>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AU7" t="inlineStr"/>
+      <c r="AV7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2014-07</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>100</v>
+      </c>
+      <c r="C8" t="n">
+        <v>13.63636363636363</v>
+      </c>
+      <c r="D8" t="n">
+        <v>11.36363636363636</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>11.36363636363636</v>
+      </c>
+      <c r="G8" t="n">
+        <v>18.18181818181818</v>
+      </c>
+      <c r="H8" t="n">
+        <v>4.545454545454546</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>18.18181818181818</v>
+      </c>
+      <c r="K8" t="n">
+        <v>4.545454545454546</v>
+      </c>
+      <c r="L8" t="n">
+        <v>15.90909090909091</v>
+      </c>
+      <c r="M8" t="n">
+        <v>15.90909090909091</v>
+      </c>
+      <c r="N8" t="n">
+        <v>11.36363636363636</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>11.36363636363636</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>9.090909090909092</v>
+      </c>
+      <c r="R8" t="n">
+        <v>13.63636363636363</v>
+      </c>
+      <c r="S8" t="n">
+        <v>15.90909090909091</v>
+      </c>
+      <c r="T8" t="n">
+        <v>4.545454545454546</v>
+      </c>
+      <c r="U8" t="n">
+        <v>4.545454545454546</v>
+      </c>
+      <c r="V8" t="n">
+        <v>9.090909090909092</v>
+      </c>
+      <c r="W8" t="n">
+        <v>11.36363636363636</v>
+      </c>
+      <c r="X8" t="n">
+        <v>13.63636363636363</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>13.63636363636363</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>9.090909090909092</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>20.45454545454546</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>15.90909090909091</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>13.63636363636363</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>25</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>22.72727272727273</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>6.818181818181817</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>15.90909090909091</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>9.090909090909092</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>13.63636363636363</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>15.90909090909091</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>20.45454545454546</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>9.090909090909092</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>13.63636363636363</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>25</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>22.72727272727273</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>29.54545454545455</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>20.45454545454546</v>
+      </c>
+      <c r="AR8" t="inlineStr"/>
+      <c r="AS8" t="inlineStr"/>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AU8" t="inlineStr"/>
+      <c r="AV8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2014-08</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>100</v>
+      </c>
+      <c r="C9" t="n">
+        <v>16.3265306122449</v>
+      </c>
+      <c r="D9" t="n">
+        <v>6.122448979591836</v>
+      </c>
+      <c r="E9" t="n">
+        <v>22.44897959183674</v>
+      </c>
+      <c r="F9" t="n">
+        <v>10.20408163265306</v>
+      </c>
+      <c r="G9" t="n">
+        <v>6.122448979591836</v>
+      </c>
+      <c r="H9" t="n">
+        <v>8.163265306122449</v>
+      </c>
+      <c r="I9" t="n">
+        <v>4.081632653061225</v>
+      </c>
+      <c r="J9" t="n">
+        <v>8.163265306122449</v>
+      </c>
+      <c r="K9" t="n">
+        <v>6.122448979591836</v>
+      </c>
+      <c r="L9" t="n">
+        <v>10.20408163265306</v>
+      </c>
+      <c r="M9" t="n">
+        <v>12.24489795918367</v>
+      </c>
+      <c r="N9" t="n">
+        <v>4.081632653061225</v>
+      </c>
+      <c r="O9" t="n">
+        <v>18.36734693877551</v>
+      </c>
+      <c r="P9" t="n">
+        <v>12.24489795918367</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>16.3265306122449</v>
+      </c>
+      <c r="R9" t="n">
+        <v>26.53061224489796</v>
+      </c>
+      <c r="S9" t="n">
+        <v>4.081632653061225</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2.040816326530612</v>
+      </c>
+      <c r="U9" t="n">
+        <v>8.163265306122449</v>
+      </c>
+      <c r="V9" t="n">
+        <v>6.122448979591836</v>
+      </c>
+      <c r="W9" t="n">
+        <v>14.28571428571428</v>
+      </c>
+      <c r="X9" t="n">
+        <v>12.24489795918367</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>14.28571428571428</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>18.36734693877551</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>30.61224489795918</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>10.20408163265306</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>22.44897959183674</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>22.44897959183674</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>4.081632653061225</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>8.163265306122449</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>6.122448979591836</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>16.3265306122449</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>14.28571428571428</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>14.28571428571428</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>18.36734693877551</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>16.3265306122449</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>18.36734693877551</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>24.48979591836735</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>22.44897959183674</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>20.40816326530612</v>
+      </c>
+      <c r="AQ9" t="inlineStr"/>
+      <c r="AR9" t="inlineStr"/>
+      <c r="AS9" t="inlineStr"/>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AU9" t="inlineStr"/>
+      <c r="AV9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2014-09</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>100</v>
+      </c>
+      <c r="C10" t="n">
+        <v>13.23529411764706</v>
+      </c>
+      <c r="D10" t="n">
+        <v>13.23529411764706</v>
+      </c>
+      <c r="E10" t="n">
+        <v>16.17647058823529</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1.470588235294118</v>
+      </c>
+      <c r="G10" t="n">
+        <v>2.941176470588235</v>
+      </c>
+      <c r="H10" t="n">
+        <v>13.23529411764706</v>
+      </c>
+      <c r="I10" t="n">
+        <v>14.70588235294118</v>
+      </c>
+      <c r="J10" t="n">
+        <v>13.23529411764706</v>
+      </c>
+      <c r="K10" t="n">
+        <v>2.941176470588235</v>
+      </c>
+      <c r="L10" t="n">
+        <v>8.823529411764707</v>
+      </c>
+      <c r="M10" t="n">
+        <v>11.76470588235294</v>
+      </c>
+      <c r="N10" t="n">
+        <v>17.64705882352941</v>
+      </c>
+      <c r="O10" t="n">
+        <v>8.823529411764707</v>
+      </c>
+      <c r="P10" t="n">
+        <v>19.11764705882353</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>22.05882352941176</v>
+      </c>
+      <c r="R10" t="n">
+        <v>2.941176470588235</v>
+      </c>
+      <c r="S10" t="n">
+        <v>7.352941176470589</v>
+      </c>
+      <c r="T10" t="n">
+        <v>13.23529411764706</v>
+      </c>
+      <c r="U10" t="n">
+        <v>7.352941176470589</v>
+      </c>
+      <c r="V10" t="n">
+        <v>13.23529411764706</v>
+      </c>
+      <c r="W10" t="n">
+        <v>11.76470588235294</v>
+      </c>
+      <c r="X10" t="n">
+        <v>10.29411764705882</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>5.88235294117647</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>17.64705882352941</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>4.411764705882353</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>22.05882352941176</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>19.11764705882353</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>4.411764705882353</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>2.941176470588235</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>13.23529411764706</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>13.23529411764706</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>11.76470588235294</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>16.17647058823529</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>19.11764705882353</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>13.23529411764706</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>22.05882352941176</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>14.70588235294118</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>23.52941176470588</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>17.64705882352941</v>
+      </c>
+      <c r="AP10" t="inlineStr"/>
+      <c r="AQ10" t="inlineStr"/>
+      <c r="AR10" t="inlineStr"/>
+      <c r="AS10" t="inlineStr"/>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AU10" t="inlineStr"/>
+      <c r="AV10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2014-10</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>100</v>
+      </c>
+      <c r="C11" t="n">
+        <v>7.142857142857142</v>
+      </c>
+      <c r="D11" t="n">
+        <v>11.9047619047619</v>
+      </c>
+      <c r="E11" t="n">
+        <v>2.380952380952381</v>
+      </c>
+      <c r="F11" t="n">
+        <v>7.142857142857142</v>
+      </c>
+      <c r="G11" t="n">
+        <v>9.523809523809524</v>
+      </c>
+      <c r="H11" t="n">
+        <v>11.9047619047619</v>
+      </c>
+      <c r="I11" t="n">
+        <v>9.523809523809524</v>
+      </c>
+      <c r="J11" t="n">
+        <v>7.142857142857142</v>
+      </c>
+      <c r="K11" t="n">
+        <v>9.523809523809524</v>
+      </c>
+      <c r="L11" t="n">
+        <v>9.523809523809524</v>
+      </c>
+      <c r="M11" t="n">
+        <v>16.66666666666666</v>
+      </c>
+      <c r="N11" t="n">
+        <v>9.523809523809524</v>
+      </c>
+      <c r="O11" t="n">
+        <v>19.04761904761905</v>
+      </c>
+      <c r="P11" t="n">
+        <v>11.9047619047619</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>4.761904761904762</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7.142857142857142</v>
+      </c>
+      <c r="S11" t="n">
+        <v>9.523809523809524</v>
+      </c>
+      <c r="T11" t="n">
+        <v>16.66666666666666</v>
+      </c>
+      <c r="U11" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="V11" t="n">
+        <v>11.9047619047619</v>
+      </c>
+      <c r="W11" t="n">
+        <v>9.523809523809524</v>
+      </c>
+      <c r="X11" t="n">
+        <v>11.9047619047619</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>23.80952380952381</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>16.66666666666666</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>11.9047619047619</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>16.66666666666666</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>7.142857142857142</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>9.523809523809524</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>14.28571428571428</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>11.9047619047619</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>16.66666666666666</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>23.80952380952381</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>19.04761904761905</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>9.523809523809524</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>26.19047619047619</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>16.66666666666666</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>30.95238095238095</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>33.33333333333333</v>
+      </c>
+      <c r="AO11" t="inlineStr"/>
+      <c r="AP11" t="inlineStr"/>
+      <c r="AQ11" t="inlineStr"/>
+      <c r="AR11" t="inlineStr"/>
+      <c r="AS11" t="inlineStr"/>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AU11" t="inlineStr"/>
+      <c r="AV11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2014-11</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>100</v>
+      </c>
+      <c r="C12" t="n">
+        <v>24.19354838709678</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>4.838709677419355</v>
+      </c>
+      <c r="F12" t="n">
+        <v>8.064516129032258</v>
+      </c>
+      <c r="G12" t="n">
+        <v>6.451612903225806</v>
+      </c>
+      <c r="H12" t="n">
+        <v>3.225806451612903</v>
+      </c>
+      <c r="I12" t="n">
+        <v>9.67741935483871</v>
+      </c>
+      <c r="J12" t="n">
+        <v>4.838709677419355</v>
+      </c>
+      <c r="K12" t="n">
+        <v>8.064516129032258</v>
+      </c>
+      <c r="L12" t="n">
+        <v>17.74193548387097</v>
+      </c>
+      <c r="M12" t="n">
+        <v>8.064516129032258</v>
+      </c>
+      <c r="N12" t="n">
+        <v>20.96774193548387</v>
+      </c>
+      <c r="O12" t="n">
+        <v>24.19354838709678</v>
+      </c>
+      <c r="P12" t="n">
+        <v>3.225806451612903</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>6.451612903225806</v>
+      </c>
+      <c r="R12" t="n">
+        <v>8.064516129032258</v>
+      </c>
+      <c r="S12" t="n">
+        <v>12.90322580645161</v>
+      </c>
+      <c r="T12" t="n">
+        <v>4.838709677419355</v>
+      </c>
+      <c r="U12" t="n">
+        <v>9.67741935483871</v>
+      </c>
+      <c r="V12" t="n">
+        <v>11.29032258064516</v>
+      </c>
+      <c r="W12" t="n">
+        <v>8.064516129032258</v>
+      </c>
+      <c r="X12" t="n">
+        <v>25.80645161290322</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>9.67741935483871</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>16.12903225806452</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>22.58064516129032</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>6.451612903225806</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>3.225806451612903</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>20.96774193548387</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>19.35483870967742</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>17.74193548387097</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>11.29032258064516</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>8.064516129032258</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>14.51612903225807</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>22.58064516129032</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>19.35483870967742</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>30.64516129032258</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>35.48387096774194</v>
+      </c>
+      <c r="AN12" t="inlineStr"/>
+      <c r="AO12" t="inlineStr"/>
+      <c r="AP12" t="inlineStr"/>
+      <c r="AQ12" t="inlineStr"/>
+      <c r="AR12" t="inlineStr"/>
+      <c r="AS12" t="inlineStr"/>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AU12" t="inlineStr"/>
+      <c r="AV12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2014-12</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>100</v>
+      </c>
+      <c r="C13" t="n">
+        <v>6.122448979591836</v>
+      </c>
+      <c r="D13" t="n">
+        <v>8.163265306122449</v>
+      </c>
+      <c r="E13" t="n">
+        <v>8.163265306122449</v>
+      </c>
+      <c r="F13" t="n">
+        <v>4.081632653061225</v>
+      </c>
+      <c r="G13" t="n">
+        <v>6.122448979591836</v>
+      </c>
+      <c r="H13" t="n">
+        <v>8.163265306122449</v>
+      </c>
+      <c r="I13" t="n">
+        <v>12.24489795918367</v>
+      </c>
+      <c r="J13" t="n">
+        <v>10.20408163265306</v>
+      </c>
+      <c r="K13" t="n">
+        <v>18.36734693877551</v>
+      </c>
+      <c r="L13" t="n">
+        <v>12.24489795918367</v>
+      </c>
+      <c r="M13" t="n">
+        <v>12.24489795918367</v>
+      </c>
+      <c r="N13" t="n">
+        <v>18.36734693877551</v>
+      </c>
+      <c r="O13" t="n">
+        <v>8.163265306122449</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2.040816326530612</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>10.20408163265306</v>
+      </c>
+      <c r="R13" t="n">
+        <v>12.24489795918367</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10.20408163265306</v>
+      </c>
+      <c r="T13" t="n">
+        <v>12.24489795918367</v>
+      </c>
+      <c r="U13" t="n">
+        <v>12.24489795918367</v>
+      </c>
+      <c r="V13" t="n">
+        <v>14.28571428571428</v>
+      </c>
+      <c r="W13" t="n">
+        <v>24.48979591836735</v>
+      </c>
+      <c r="X13" t="n">
+        <v>8.163265306122449</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>24.48979591836735</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>24.48979591836735</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>8.163265306122449</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>6.122448979591836</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>8.163265306122449</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>10.20408163265306</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>16.3265306122449</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>14.28571428571428</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>14.28571428571428</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>18.36734693877551</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>20.40816326530612</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>18.36734693877551</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>30.61224489795918</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>30.61224489795918</v>
+      </c>
+      <c r="AM13" t="inlineStr"/>
+      <c r="AN13" t="inlineStr"/>
+      <c r="AO13" t="inlineStr"/>
+      <c r="AP13" t="inlineStr"/>
+      <c r="AQ13" t="inlineStr"/>
+      <c r="AR13" t="inlineStr"/>
+      <c r="AS13" t="inlineStr"/>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AU13" t="inlineStr"/>
+      <c r="AV13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2015-01</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>100</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" t="n">
+        <v>14.28571428571428</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>14.28571428571428</v>
+      </c>
+      <c r="G14" t="n">
+        <v>14.28571428571428</v>
+      </c>
+      <c r="H14" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>14.28571428571428</v>
+      </c>
+      <c r="L14" t="n">
+        <v>14.28571428571428</v>
+      </c>
+      <c r="M14" t="n">
+        <v>14.28571428571428</v>
+      </c>
+      <c r="N14" t="n">
+        <v>14.28571428571428</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>14.28571428571428</v>
+      </c>
+      <c r="R14" t="n">
+        <v>14.28571428571428</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" t="n">
+        <v>14.28571428571428</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
+        <v>14.28571428571428</v>
+      </c>
+      <c r="X14" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>14.28571428571428</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>14.28571428571428</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>14.28571428571428</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>14.28571428571428</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>14.28571428571428</v>
+      </c>
+      <c r="AL14" t="inlineStr"/>
+      <c r="AM14" t="inlineStr"/>
+      <c r="AN14" t="inlineStr"/>
+      <c r="AO14" t="inlineStr"/>
+      <c r="AP14" t="inlineStr"/>
+      <c r="AQ14" t="inlineStr"/>
+      <c r="AR14" t="inlineStr"/>
+      <c r="AS14" t="inlineStr"/>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AU14" t="inlineStr"/>
+      <c r="AV14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2015-02</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>100</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" t="n">
+        <v>14.28571428571428</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>14.28571428571428</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>14.28571428571428</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>14.28571428571428</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="n">
+        <v>14.28571428571428</v>
+      </c>
+      <c r="V15" t="n">
+        <v>14.28571428571428</v>
+      </c>
+      <c r="W15" t="n">
+        <v>14.28571428571428</v>
+      </c>
+      <c r="X15" t="n">
+        <v>14.28571428571428</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>14.28571428571428</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>14.28571428571428</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>57.14285714285714</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>14.28571428571428</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="AK15" t="inlineStr"/>
+      <c r="AL15" t="inlineStr"/>
+      <c r="AM15" t="inlineStr"/>
+      <c r="AN15" t="inlineStr"/>
+      <c r="AO15" t="inlineStr"/>
+      <c r="AP15" t="inlineStr"/>
+      <c r="AQ15" t="inlineStr"/>
+      <c r="AR15" t="inlineStr"/>
+      <c r="AS15" t="inlineStr"/>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AU15" t="inlineStr"/>
+      <c r="AV15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2015-03</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>100</v>
+      </c>
+      <c r="C16" t="n">
+        <v>5.555555555555555</v>
+      </c>
+      <c r="D16" t="n">
+        <v>5.555555555555555</v>
+      </c>
+      <c r="E16" t="n">
+        <v>16.66666666666666</v>
+      </c>
+      <c r="F16" t="n">
+        <v>5.555555555555555</v>
+      </c>
+      <c r="G16" t="n">
+        <v>5.555555555555555</v>
+      </c>
+      <c r="H16" t="n">
+        <v>16.66666666666666</v>
+      </c>
+      <c r="I16" t="n">
+        <v>5.555555555555555</v>
+      </c>
+      <c r="J16" t="n">
+        <v>16.66666666666666</v>
+      </c>
+      <c r="K16" t="n">
+        <v>5.555555555555555</v>
+      </c>
+      <c r="L16" t="n">
+        <v>5.555555555555555</v>
+      </c>
+      <c r="M16" t="n">
+        <v>11.11111111111111</v>
+      </c>
+      <c r="N16" t="n">
+        <v>5.555555555555555</v>
+      </c>
+      <c r="O16" t="n">
+        <v>5.555555555555555</v>
+      </c>
+      <c r="P16" t="n">
+        <v>16.66666666666666</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>11.11111111111111</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>11.11111111111111</v>
+      </c>
+      <c r="T16" t="n">
+        <v>38.88888888888889</v>
+      </c>
+      <c r="U16" t="n">
+        <v>16.66666666666666</v>
+      </c>
+      <c r="V16" t="n">
+        <v>33.33333333333333</v>
+      </c>
+      <c r="W16" t="n">
+        <v>27.77777777777778</v>
+      </c>
+      <c r="X16" t="n">
+        <v>33.33333333333333</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>5.555555555555555</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>5.555555555555555</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>11.11111111111111</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>11.11111111111111</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>5.555555555555555</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>22.22222222222222</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>22.22222222222222</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>27.77777777777778</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>22.22222222222222</v>
+      </c>
+      <c r="AJ16" t="inlineStr"/>
+      <c r="AK16" t="inlineStr"/>
+      <c r="AL16" t="inlineStr"/>
+      <c r="AM16" t="inlineStr"/>
+      <c r="AN16" t="inlineStr"/>
+      <c r="AO16" t="inlineStr"/>
+      <c r="AP16" t="inlineStr"/>
+      <c r="AQ16" t="inlineStr"/>
+      <c r="AR16" t="inlineStr"/>
+      <c r="AS16" t="inlineStr"/>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AU16" t="inlineStr"/>
+      <c r="AV16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2015-04</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>100</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="n">
+        <v>8.333333333333332</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>8.333333333333332</v>
+      </c>
+      <c r="H17" t="n">
+        <v>25</v>
+      </c>
+      <c r="I17" t="n">
+        <v>16.66666666666666</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>8.333333333333332</v>
+      </c>
+      <c r="M17" t="n">
+        <v>8.333333333333332</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>8.333333333333332</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>25</v>
+      </c>
+      <c r="R17" t="n">
+        <v>8.333333333333332</v>
+      </c>
+      <c r="S17" t="n">
+        <v>50</v>
+      </c>
+      <c r="T17" t="n">
+        <v>8.333333333333332</v>
+      </c>
+      <c r="U17" t="n">
+        <v>16.66666666666666</v>
+      </c>
+      <c r="V17" t="n">
+        <v>16.66666666666666</v>
+      </c>
+      <c r="W17" t="n">
+        <v>16.66666666666666</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>8.333333333333332</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>16.66666666666666</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>25</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>8.333333333333332</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>33.33333333333333</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>33.33333333333333</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>8.333333333333332</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI17" t="inlineStr"/>
+      <c r="AJ17" t="inlineStr"/>
+      <c r="AK17" t="inlineStr"/>
+      <c r="AL17" t="inlineStr"/>
+      <c r="AM17" t="inlineStr"/>
+      <c r="AN17" t="inlineStr"/>
+      <c r="AO17" t="inlineStr"/>
+      <c r="AP17" t="inlineStr"/>
+      <c r="AQ17" t="inlineStr"/>
+      <c r="AR17" t="inlineStr"/>
+      <c r="AS17" t="inlineStr"/>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AU17" t="inlineStr"/>
+      <c r="AV17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2015-05</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>100</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" t="n">
+        <v>8.333333333333332</v>
+      </c>
+      <c r="F18" t="n">
+        <v>16.66666666666666</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
+        <v>16.66666666666666</v>
+      </c>
+      <c r="I18" t="n">
+        <v>16.66666666666666</v>
+      </c>
+      <c r="J18" t="n">
+        <v>8.333333333333332</v>
+      </c>
+      <c r="K18" t="n">
+        <v>8.333333333333332</v>
+      </c>
+      <c r="L18" t="n">
+        <v>25</v>
+      </c>
+      <c r="M18" t="n">
+        <v>16.66666666666666</v>
+      </c>
+      <c r="N18" t="n">
+        <v>8.333333333333332</v>
+      </c>
+      <c r="O18" t="n">
+        <v>16.66666666666666</v>
+      </c>
+      <c r="P18" t="n">
+        <v>8.333333333333332</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>25</v>
+      </c>
+      <c r="R18" t="n">
+        <v>25</v>
+      </c>
+      <c r="S18" t="n">
+        <v>16.66666666666666</v>
+      </c>
+      <c r="T18" t="n">
+        <v>16.66666666666666</v>
+      </c>
+      <c r="U18" t="n">
+        <v>8.333333333333332</v>
+      </c>
+      <c r="V18" t="n">
+        <v>8.333333333333332</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>8.333333333333332</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>25</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>8.333333333333332</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>50</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>16.66666666666666</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>25</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>16.66666666666666</v>
+      </c>
+      <c r="AH18" t="inlineStr"/>
+      <c r="AI18" t="inlineStr"/>
+      <c r="AJ18" t="inlineStr"/>
+      <c r="AK18" t="inlineStr"/>
+      <c r="AL18" t="inlineStr"/>
+      <c r="AM18" t="inlineStr"/>
+      <c r="AN18" t="inlineStr"/>
+      <c r="AO18" t="inlineStr"/>
+      <c r="AP18" t="inlineStr"/>
+      <c r="AQ18" t="inlineStr"/>
+      <c r="AR18" t="inlineStr"/>
+      <c r="AS18" t="inlineStr"/>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AU18" t="inlineStr"/>
+      <c r="AV18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2015-06</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>100</v>
+      </c>
+      <c r="C19" t="n">
+        <v>8.333333333333332</v>
+      </c>
+      <c r="D19" t="n">
+        <v>8.333333333333332</v>
+      </c>
+      <c r="E19" t="n">
+        <v>41.66666666666667</v>
+      </c>
+      <c r="F19" t="n">
+        <v>8.333333333333332</v>
+      </c>
+      <c r="G19" t="n">
+        <v>25</v>
+      </c>
+      <c r="H19" t="n">
+        <v>16.66666666666666</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>8.333333333333332</v>
+      </c>
+      <c r="K19" t="n">
+        <v>25</v>
+      </c>
+      <c r="L19" t="n">
+        <v>8.333333333333332</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>41.66666666666667</v>
+      </c>
+      <c r="O19" t="n">
+        <v>8.333333333333332</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>16.66666666666666</v>
+      </c>
+      <c r="R19" t="n">
+        <v>25</v>
+      </c>
+      <c r="S19" t="n">
+        <v>25</v>
+      </c>
+      <c r="T19" t="n">
+        <v>16.66666666666666</v>
+      </c>
+      <c r="U19" t="n">
+        <v>8.333333333333332</v>
+      </c>
+      <c r="V19" t="n">
+        <v>8.333333333333332</v>
+      </c>
+      <c r="W19" t="n">
+        <v>41.66666666666667</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>8.333333333333332</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>16.66666666666666</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>16.66666666666666</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>25</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>16.66666666666666</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>33.33333333333333</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>25</v>
+      </c>
+      <c r="AG19" t="inlineStr"/>
+      <c r="AH19" t="inlineStr"/>
+      <c r="AI19" t="inlineStr"/>
+      <c r="AJ19" t="inlineStr"/>
+      <c r="AK19" t="inlineStr"/>
+      <c r="AL19" t="inlineStr"/>
+      <c r="AM19" t="inlineStr"/>
+      <c r="AN19" t="inlineStr"/>
+      <c r="AO19" t="inlineStr"/>
+      <c r="AP19" t="inlineStr"/>
+      <c r="AQ19" t="inlineStr"/>
+      <c r="AR19" t="inlineStr"/>
+      <c r="AS19" t="inlineStr"/>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AU19" t="inlineStr"/>
+      <c r="AV19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2015-07</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>100</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" t="n">
+        <v>25</v>
+      </c>
+      <c r="F20" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="G20" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>25</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="N20" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="R20" t="n">
+        <v>25</v>
+      </c>
+      <c r="S20" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="T20" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="W20" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="X20" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>25</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>25</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>25</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="inlineStr"/>
+      <c r="AH20" t="inlineStr"/>
+      <c r="AI20" t="inlineStr"/>
+      <c r="AJ20" t="inlineStr"/>
+      <c r="AK20" t="inlineStr"/>
+      <c r="AL20" t="inlineStr"/>
+      <c r="AM20" t="inlineStr"/>
+      <c r="AN20" t="inlineStr"/>
+      <c r="AO20" t="inlineStr"/>
+      <c r="AP20" t="inlineStr"/>
+      <c r="AQ20" t="inlineStr"/>
+      <c r="AR20" t="inlineStr"/>
+      <c r="AS20" t="inlineStr"/>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AU20" t="inlineStr"/>
+      <c r="AV20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2015-08</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>100</v>
+      </c>
+      <c r="C21" t="n">
+        <v>25</v>
+      </c>
+      <c r="D21" t="n">
+        <v>8.333333333333332</v>
+      </c>
+      <c r="E21" t="n">
+        <v>16.66666666666666</v>
+      </c>
+      <c r="F21" t="n">
+        <v>25</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>8.333333333333332</v>
+      </c>
+      <c r="L21" t="n">
+        <v>16.66666666666666</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>33.33333333333333</v>
+      </c>
+      <c r="P21" t="n">
+        <v>16.66666666666666</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>25</v>
+      </c>
+      <c r="R21" t="n">
+        <v>25</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>8.333333333333332</v>
+      </c>
+      <c r="U21" t="n">
+        <v>16.66666666666666</v>
+      </c>
+      <c r="V21" t="n">
+        <v>41.66666666666667</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0</v>
+      </c>
+      <c r="X21" t="n">
+        <v>16.66666666666666</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>25</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>8.333333333333332</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>41.66666666666667</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>16.66666666666666</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>25</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>16.66666666666666</v>
+      </c>
+      <c r="AE21" t="inlineStr"/>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="inlineStr"/>
+      <c r="AH21" t="inlineStr"/>
+      <c r="AI21" t="inlineStr"/>
+      <c r="AJ21" t="inlineStr"/>
+      <c r="AK21" t="inlineStr"/>
+      <c r="AL21" t="inlineStr"/>
+      <c r="AM21" t="inlineStr"/>
+      <c r="AN21" t="inlineStr"/>
+      <c r="AO21" t="inlineStr"/>
+      <c r="AP21" t="inlineStr"/>
+      <c r="AQ21" t="inlineStr"/>
+      <c r="AR21" t="inlineStr"/>
+      <c r="AS21" t="inlineStr"/>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AU21" t="inlineStr"/>
+      <c r="AV21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2015-09</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>100</v>
+      </c>
+      <c r="C22" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="D22" t="n">
+        <v>18.75</v>
+      </c>
+      <c r="E22" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="F22" t="n">
+        <v>25</v>
+      </c>
+      <c r="G22" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="H22" t="n">
+        <v>18.75</v>
+      </c>
+      <c r="I22" t="n">
+        <v>18.75</v>
+      </c>
+      <c r="J22" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="M22" t="n">
+        <v>43.75</v>
+      </c>
+      <c r="N22" t="n">
+        <v>18.75</v>
+      </c>
+      <c r="O22" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="P22" t="n">
+        <v>18.75</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="T22" t="n">
+        <v>25</v>
+      </c>
+      <c r="U22" t="n">
+        <v>31.25</v>
+      </c>
+      <c r="V22" t="n">
+        <v>25</v>
+      </c>
+      <c r="W22" t="n">
+        <v>18.75</v>
+      </c>
+      <c r="X22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>25</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>43.75</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>25</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>25</v>
+      </c>
+      <c r="AD22" t="inlineStr"/>
+      <c r="AE22" t="inlineStr"/>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="inlineStr"/>
+      <c r="AH22" t="inlineStr"/>
+      <c r="AI22" t="inlineStr"/>
+      <c r="AJ22" t="inlineStr"/>
+      <c r="AK22" t="inlineStr"/>
+      <c r="AL22" t="inlineStr"/>
+      <c r="AM22" t="inlineStr"/>
+      <c r="AN22" t="inlineStr"/>
+      <c r="AO22" t="inlineStr"/>
+      <c r="AP22" t="inlineStr"/>
+      <c r="AQ22" t="inlineStr"/>
+      <c r="AR22" t="inlineStr"/>
+      <c r="AS22" t="inlineStr"/>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AU22" t="inlineStr"/>
+      <c r="AV22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2015-10</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>100</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" t="n">
+        <v>44.44444444444444</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
+        <v>11.11111111111111</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>11.11111111111111</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>11.11111111111111</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>11.11111111111111</v>
+      </c>
+      <c r="P23" t="n">
+        <v>11.11111111111111</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>22.22222222222222</v>
+      </c>
+      <c r="R23" t="n">
+        <v>11.11111111111111</v>
+      </c>
+      <c r="S23" t="n">
+        <v>11.11111111111111</v>
+      </c>
+      <c r="T23" t="n">
+        <v>33.33333333333333</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0</v>
+      </c>
+      <c r="W23" t="n">
+        <v>22.22222222222222</v>
+      </c>
+      <c r="X23" t="n">
+        <v>11.11111111111111</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>22.22222222222222</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>11.11111111111111</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>11.11111111111111</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>33.33333333333333</v>
+      </c>
+      <c r="AC23" t="inlineStr"/>
+      <c r="AD23" t="inlineStr"/>
+      <c r="AE23" t="inlineStr"/>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="inlineStr"/>
+      <c r="AH23" t="inlineStr"/>
+      <c r="AI23" t="inlineStr"/>
+      <c r="AJ23" t="inlineStr"/>
+      <c r="AK23" t="inlineStr"/>
+      <c r="AL23" t="inlineStr"/>
+      <c r="AM23" t="inlineStr"/>
+      <c r="AN23" t="inlineStr"/>
+      <c r="AO23" t="inlineStr"/>
+      <c r="AP23" t="inlineStr"/>
+      <c r="AQ23" t="inlineStr"/>
+      <c r="AR23" t="inlineStr"/>
+      <c r="AS23" t="inlineStr"/>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AU23" t="inlineStr"/>
+      <c r="AV23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2015-11</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>100</v>
+      </c>
+      <c r="C24" t="n">
+        <v>10</v>
+      </c>
+      <c r="D24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>10</v>
+      </c>
+      <c r="I24" t="n">
+        <v>10</v>
+      </c>
+      <c r="J24" t="n">
+        <v>20</v>
+      </c>
+      <c r="K24" t="n">
+        <v>10</v>
+      </c>
+      <c r="L24" t="n">
+        <v>10</v>
+      </c>
+      <c r="M24" t="n">
+        <v>20</v>
+      </c>
+      <c r="N24" t="n">
+        <v>10</v>
+      </c>
+      <c r="O24" t="n">
+        <v>20</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>20</v>
+      </c>
+      <c r="R24" t="n">
+        <v>30</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" t="n">
+        <v>0</v>
+      </c>
+      <c r="W24" t="n">
+        <v>20</v>
+      </c>
+      <c r="X24" t="n">
+        <v>40</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>50</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>50</v>
+      </c>
+      <c r="AB24" t="inlineStr"/>
+      <c r="AC24" t="inlineStr"/>
+      <c r="AD24" t="inlineStr"/>
+      <c r="AE24" t="inlineStr"/>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="inlineStr"/>
+      <c r="AH24" t="inlineStr"/>
+      <c r="AI24" t="inlineStr"/>
+      <c r="AJ24" t="inlineStr"/>
+      <c r="AK24" t="inlineStr"/>
+      <c r="AL24" t="inlineStr"/>
+      <c r="AM24" t="inlineStr"/>
+      <c r="AN24" t="inlineStr"/>
+      <c r="AO24" t="inlineStr"/>
+      <c r="AP24" t="inlineStr"/>
+      <c r="AQ24" t="inlineStr"/>
+      <c r="AR24" t="inlineStr"/>
+      <c r="AS24" t="inlineStr"/>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AU24" t="inlineStr"/>
+      <c r="AV24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2015-12</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>100</v>
+      </c>
+      <c r="C25" t="n">
+        <v>7.692307692307693</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" t="n">
+        <v>7.692307692307693</v>
+      </c>
+      <c r="F25" t="n">
+        <v>15.38461538461539</v>
+      </c>
+      <c r="G25" t="n">
+        <v>15.38461538461539</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>23.07692307692308</v>
+      </c>
+      <c r="J25" t="n">
+        <v>7.692307692307693</v>
+      </c>
+      <c r="K25" t="n">
+        <v>23.07692307692308</v>
+      </c>
+      <c r="L25" t="n">
+        <v>15.38461538461539</v>
+      </c>
+      <c r="M25" t="n">
+        <v>15.38461538461539</v>
+      </c>
+      <c r="N25" t="n">
+        <v>7.692307692307693</v>
+      </c>
+      <c r="O25" t="n">
+        <v>7.692307692307693</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>23.07692307692308</v>
+      </c>
+      <c r="R25" t="n">
+        <v>15.38461538461539</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>7.692307692307693</v>
+      </c>
+      <c r="U25" t="n">
+        <v>15.38461538461539</v>
+      </c>
+      <c r="V25" t="n">
+        <v>15.38461538461539</v>
+      </c>
+      <c r="W25" t="n">
+        <v>7.692307692307693</v>
+      </c>
+      <c r="X25" t="n">
+        <v>7.692307692307693</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>30.76923076923077</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>23.07692307692308</v>
+      </c>
+      <c r="AA25" t="inlineStr"/>
+      <c r="AB25" t="inlineStr"/>
+      <c r="AC25" t="inlineStr"/>
+      <c r="AD25" t="inlineStr"/>
+      <c r="AE25" t="inlineStr"/>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="inlineStr"/>
+      <c r="AH25" t="inlineStr"/>
+      <c r="AI25" t="inlineStr"/>
+      <c r="AJ25" t="inlineStr"/>
+      <c r="AK25" t="inlineStr"/>
+      <c r="AL25" t="inlineStr"/>
+      <c r="AM25" t="inlineStr"/>
+      <c r="AN25" t="inlineStr"/>
+      <c r="AO25" t="inlineStr"/>
+      <c r="AP25" t="inlineStr"/>
+      <c r="AQ25" t="inlineStr"/>
+      <c r="AR25" t="inlineStr"/>
+      <c r="AS25" t="inlineStr"/>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AU25" t="inlineStr"/>
+      <c r="AV25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2016-01</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>100</v>
+      </c>
+      <c r="C26" t="n">
+        <v>16.66666666666666</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" t="n">
+        <v>16.66666666666666</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="n">
+        <v>16.66666666666666</v>
+      </c>
+      <c r="H26" t="n">
+        <v>16.66666666666666</v>
+      </c>
+      <c r="I26" t="n">
+        <v>16.66666666666666</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
+        <v>16.66666666666666</v>
+      </c>
+      <c r="L26" t="n">
+        <v>16.66666666666666</v>
+      </c>
+      <c r="M26" t="n">
+        <v>16.66666666666666</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>16.66666666666666</v>
+      </c>
+      <c r="P26" t="n">
+        <v>33.33333333333333</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" t="n">
+        <v>33.33333333333333</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>33.33333333333333</v>
+      </c>
+      <c r="U26" t="n">
+        <v>33.33333333333333</v>
+      </c>
+      <c r="V26" t="n">
+        <v>33.33333333333333</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X26" t="n">
+        <v>16.66666666666666</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>33.33333333333333</v>
+      </c>
+      <c r="Z26" t="inlineStr"/>
+      <c r="AA26" t="inlineStr"/>
+      <c r="AB26" t="inlineStr"/>
+      <c r="AC26" t="inlineStr"/>
+      <c r="AD26" t="inlineStr"/>
+      <c r="AE26" t="inlineStr"/>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="inlineStr"/>
+      <c r="AH26" t="inlineStr"/>
+      <c r="AI26" t="inlineStr"/>
+      <c r="AJ26" t="inlineStr"/>
+      <c r="AK26" t="inlineStr"/>
+      <c r="AL26" t="inlineStr"/>
+      <c r="AM26" t="inlineStr"/>
+      <c r="AN26" t="inlineStr"/>
+      <c r="AO26" t="inlineStr"/>
+      <c r="AP26" t="inlineStr"/>
+      <c r="AQ26" t="inlineStr"/>
+      <c r="AR26" t="inlineStr"/>
+      <c r="AS26" t="inlineStr"/>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AU26" t="inlineStr"/>
+      <c r="AV26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2016-02</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>100</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" t="n">
+        <v>50</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="n">
+        <v>50</v>
+      </c>
+      <c r="K27" t="n">
+        <v>50</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>50</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>50</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>50</v>
+      </c>
+      <c r="U27" t="n">
+        <v>100</v>
+      </c>
+      <c r="V27" t="n">
+        <v>0</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0</v>
+      </c>
+      <c r="X27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y27" t="inlineStr"/>
+      <c r="Z27" t="inlineStr"/>
+      <c r="AA27" t="inlineStr"/>
+      <c r="AB27" t="inlineStr"/>
+      <c r="AC27" t="inlineStr"/>
+      <c r="AD27" t="inlineStr"/>
+      <c r="AE27" t="inlineStr"/>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="inlineStr"/>
+      <c r="AH27" t="inlineStr"/>
+      <c r="AI27" t="inlineStr"/>
+      <c r="AJ27" t="inlineStr"/>
+      <c r="AK27" t="inlineStr"/>
+      <c r="AL27" t="inlineStr"/>
+      <c r="AM27" t="inlineStr"/>
+      <c r="AN27" t="inlineStr"/>
+      <c r="AO27" t="inlineStr"/>
+      <c r="AP27" t="inlineStr"/>
+      <c r="AQ27" t="inlineStr"/>
+      <c r="AR27" t="inlineStr"/>
+      <c r="AS27" t="inlineStr"/>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AU27" t="inlineStr"/>
+      <c r="AV27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2016-03</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>100</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" t="n">
+        <v>50</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" t="n">
+        <v>50</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" t="n">
+        <v>16.66666666666666</v>
+      </c>
+      <c r="I28" t="n">
+        <v>16.66666666666666</v>
+      </c>
+      <c r="J28" t="n">
+        <v>16.66666666666666</v>
+      </c>
+      <c r="K28" t="n">
+        <v>16.66666666666666</v>
+      </c>
+      <c r="L28" t="n">
+        <v>50</v>
+      </c>
+      <c r="M28" t="n">
+        <v>16.66666666666666</v>
+      </c>
+      <c r="N28" t="n">
+        <v>16.66666666666666</v>
+      </c>
+      <c r="O28" t="n">
+        <v>33.33333333333333</v>
+      </c>
+      <c r="P28" t="n">
+        <v>33.33333333333333</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>16.66666666666666</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" t="n">
+        <v>16.66666666666666</v>
+      </c>
+      <c r="T28" t="n">
+        <v>16.66666666666666</v>
+      </c>
+      <c r="U28" t="n">
+        <v>16.66666666666666</v>
+      </c>
+      <c r="V28" t="n">
+        <v>66.66666666666666</v>
+      </c>
+      <c r="W28" t="n">
+        <v>33.33333333333333</v>
+      </c>
+      <c r="X28" t="inlineStr"/>
+      <c r="Y28" t="inlineStr"/>
+      <c r="Z28" t="inlineStr"/>
+      <c r="AA28" t="inlineStr"/>
+      <c r="AB28" t="inlineStr"/>
+      <c r="AC28" t="inlineStr"/>
+      <c r="AD28" t="inlineStr"/>
+      <c r="AE28" t="inlineStr"/>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="inlineStr"/>
+      <c r="AH28" t="inlineStr"/>
+      <c r="AI28" t="inlineStr"/>
+      <c r="AJ28" t="inlineStr"/>
+      <c r="AK28" t="inlineStr"/>
+      <c r="AL28" t="inlineStr"/>
+      <c r="AM28" t="inlineStr"/>
+      <c r="AN28" t="inlineStr"/>
+      <c r="AO28" t="inlineStr"/>
+      <c r="AP28" t="inlineStr"/>
+      <c r="AQ28" t="inlineStr"/>
+      <c r="AR28" t="inlineStr"/>
+      <c r="AS28" t="inlineStr"/>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AU28" t="inlineStr"/>
+      <c r="AV28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2016-04</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>100</v>
+      </c>
+      <c r="C29" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" t="n">
+        <v>14.28571428571428</v>
+      </c>
+      <c r="F29" t="n">
+        <v>14.28571428571428</v>
+      </c>
+      <c r="G29" t="n">
+        <v>57.14285714285714</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="n">
+        <v>14.28571428571428</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>14.28571428571428</v>
+      </c>
+      <c r="N29" t="n">
+        <v>14.28571428571428</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="T29" t="n">
+        <v>14.28571428571428</v>
+      </c>
+      <c r="U29" t="n">
+        <v>14.28571428571428</v>
+      </c>
+      <c r="V29" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="W29" t="inlineStr"/>
+      <c r="X29" t="inlineStr"/>
+      <c r="Y29" t="inlineStr"/>
+      <c r="Z29" t="inlineStr"/>
+      <c r="AA29" t="inlineStr"/>
+      <c r="AB29" t="inlineStr"/>
+      <c r="AC29" t="inlineStr"/>
+      <c r="AD29" t="inlineStr"/>
+      <c r="AE29" t="inlineStr"/>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="inlineStr"/>
+      <c r="AH29" t="inlineStr"/>
+      <c r="AI29" t="inlineStr"/>
+      <c r="AJ29" t="inlineStr"/>
+      <c r="AK29" t="inlineStr"/>
+      <c r="AL29" t="inlineStr"/>
+      <c r="AM29" t="inlineStr"/>
+      <c r="AN29" t="inlineStr"/>
+      <c r="AO29" t="inlineStr"/>
+      <c r="AP29" t="inlineStr"/>
+      <c r="AQ29" t="inlineStr"/>
+      <c r="AR29" t="inlineStr"/>
+      <c r="AS29" t="inlineStr"/>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AU29" t="inlineStr"/>
+      <c r="AV29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2016-05</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>100</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" t="n">
+        <v>14.28571428571428</v>
+      </c>
+      <c r="E30" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="F30" t="n">
+        <v>14.28571428571428</v>
+      </c>
+      <c r="G30" t="n">
+        <v>14.28571428571428</v>
+      </c>
+      <c r="H30" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="I30" t="n">
+        <v>14.28571428571428</v>
+      </c>
+      <c r="J30" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="K30" t="n">
+        <v>14.28571428571428</v>
+      </c>
+      <c r="L30" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="M30" t="n">
+        <v>14.28571428571428</v>
+      </c>
+      <c r="N30" t="n">
+        <v>14.28571428571428</v>
+      </c>
+      <c r="O30" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>0</v>
+      </c>
+      <c r="R30" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="S30" t="n">
+        <v>14.28571428571428</v>
+      </c>
+      <c r="T30" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="U30" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="V30" t="inlineStr"/>
+      <c r="W30" t="inlineStr"/>
+      <c r="X30" t="inlineStr"/>
+      <c r="Y30" t="inlineStr"/>
+      <c r="Z30" t="inlineStr"/>
+      <c r="AA30" t="inlineStr"/>
+      <c r="AB30" t="inlineStr"/>
+      <c r="AC30" t="inlineStr"/>
+      <c r="AD30" t="inlineStr"/>
+      <c r="AE30" t="inlineStr"/>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="inlineStr"/>
+      <c r="AH30" t="inlineStr"/>
+      <c r="AI30" t="inlineStr"/>
+      <c r="AJ30" t="inlineStr"/>
+      <c r="AK30" t="inlineStr"/>
+      <c r="AL30" t="inlineStr"/>
+      <c r="AM30" t="inlineStr"/>
+      <c r="AN30" t="inlineStr"/>
+      <c r="AO30" t="inlineStr"/>
+      <c r="AP30" t="inlineStr"/>
+      <c r="AQ30" t="inlineStr"/>
+      <c r="AR30" t="inlineStr"/>
+      <c r="AS30" t="inlineStr"/>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AU30" t="inlineStr"/>
+      <c r="AV30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2016-06</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>100</v>
+      </c>
+      <c r="C31" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="D31" t="n">
+        <v>25</v>
+      </c>
+      <c r="E31" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="F31" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="G31" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="H31" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="I31" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="n">
+        <v>25</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="n">
+        <v>25</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="T31" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="U31" t="inlineStr"/>
+      <c r="V31" t="inlineStr"/>
+      <c r="W31" t="inlineStr"/>
+      <c r="X31" t="inlineStr"/>
+      <c r="Y31" t="inlineStr"/>
+      <c r="Z31" t="inlineStr"/>
+      <c r="AA31" t="inlineStr"/>
+      <c r="AB31" t="inlineStr"/>
+      <c r="AC31" t="inlineStr"/>
+      <c r="AD31" t="inlineStr"/>
+      <c r="AE31" t="inlineStr"/>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="inlineStr"/>
+      <c r="AH31" t="inlineStr"/>
+      <c r="AI31" t="inlineStr"/>
+      <c r="AJ31" t="inlineStr"/>
+      <c r="AK31" t="inlineStr"/>
+      <c r="AL31" t="inlineStr"/>
+      <c r="AM31" t="inlineStr"/>
+      <c r="AN31" t="inlineStr"/>
+      <c r="AO31" t="inlineStr"/>
+      <c r="AP31" t="inlineStr"/>
+      <c r="AQ31" t="inlineStr"/>
+      <c r="AR31" t="inlineStr"/>
+      <c r="AS31" t="inlineStr"/>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AU31" t="inlineStr"/>
+      <c r="AV31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2016-07</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>100</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="n">
+        <v>50</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>0</v>
+      </c>
+      <c r="R32" t="n">
+        <v>50</v>
+      </c>
+      <c r="S32" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" t="inlineStr"/>
+      <c r="U32" t="inlineStr"/>
+      <c r="V32" t="inlineStr"/>
+      <c r="W32" t="inlineStr"/>
+      <c r="X32" t="inlineStr"/>
+      <c r="Y32" t="inlineStr"/>
+      <c r="Z32" t="inlineStr"/>
+      <c r="AA32" t="inlineStr"/>
+      <c r="AB32" t="inlineStr"/>
+      <c r="AC32" t="inlineStr"/>
+      <c r="AD32" t="inlineStr"/>
+      <c r="AE32" t="inlineStr"/>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="inlineStr"/>
+      <c r="AH32" t="inlineStr"/>
+      <c r="AI32" t="inlineStr"/>
+      <c r="AJ32" t="inlineStr"/>
+      <c r="AK32" t="inlineStr"/>
+      <c r="AL32" t="inlineStr"/>
+      <c r="AM32" t="inlineStr"/>
+      <c r="AN32" t="inlineStr"/>
+      <c r="AO32" t="inlineStr"/>
+      <c r="AP32" t="inlineStr"/>
+      <c r="AQ32" t="inlineStr"/>
+      <c r="AR32" t="inlineStr"/>
+      <c r="AS32" t="inlineStr"/>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AU32" t="inlineStr"/>
+      <c r="AV32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2016-08</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>100</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" t="n">
+        <v>25</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" t="n">
+        <v>25</v>
+      </c>
+      <c r="J33" t="n">
+        <v>50</v>
+      </c>
+      <c r="K33" t="n">
+        <v>50</v>
+      </c>
+      <c r="L33" t="n">
+        <v>25</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" t="n">
+        <v>25</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>50</v>
+      </c>
+      <c r="R33" t="n">
+        <v>75</v>
+      </c>
+      <c r="S33" t="inlineStr"/>
+      <c r="T33" t="inlineStr"/>
+      <c r="U33" t="inlineStr"/>
+      <c r="V33" t="inlineStr"/>
+      <c r="W33" t="inlineStr"/>
+      <c r="X33" t="inlineStr"/>
+      <c r="Y33" t="inlineStr"/>
+      <c r="Z33" t="inlineStr"/>
+      <c r="AA33" t="inlineStr"/>
+      <c r="AB33" t="inlineStr"/>
+      <c r="AC33" t="inlineStr"/>
+      <c r="AD33" t="inlineStr"/>
+      <c r="AE33" t="inlineStr"/>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="inlineStr"/>
+      <c r="AH33" t="inlineStr"/>
+      <c r="AI33" t="inlineStr"/>
+      <c r="AJ33" t="inlineStr"/>
+      <c r="AK33" t="inlineStr"/>
+      <c r="AL33" t="inlineStr"/>
+      <c r="AM33" t="inlineStr"/>
+      <c r="AN33" t="inlineStr"/>
+      <c r="AO33" t="inlineStr"/>
+      <c r="AP33" t="inlineStr"/>
+      <c r="AQ33" t="inlineStr"/>
+      <c r="AR33" t="inlineStr"/>
+      <c r="AS33" t="inlineStr"/>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AU33" t="inlineStr"/>
+      <c r="AV33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2016-10</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>100</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" t="n">
+        <v>100</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" t="n">
+        <v>100</v>
+      </c>
+      <c r="M34" t="n">
+        <v>100</v>
+      </c>
+      <c r="N34" t="n">
+        <v>100</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q34" t="inlineStr"/>
+      <c r="R34" t="inlineStr"/>
+      <c r="S34" t="inlineStr"/>
+      <c r="T34" t="inlineStr"/>
+      <c r="U34" t="inlineStr"/>
+      <c r="V34" t="inlineStr"/>
+      <c r="W34" t="inlineStr"/>
+      <c r="X34" t="inlineStr"/>
+      <c r="Y34" t="inlineStr"/>
+      <c r="Z34" t="inlineStr"/>
+      <c r="AA34" t="inlineStr"/>
+      <c r="AB34" t="inlineStr"/>
+      <c r="AC34" t="inlineStr"/>
+      <c r="AD34" t="inlineStr"/>
+      <c r="AE34" t="inlineStr"/>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="inlineStr"/>
+      <c r="AH34" t="inlineStr"/>
+      <c r="AI34" t="inlineStr"/>
+      <c r="AJ34" t="inlineStr"/>
+      <c r="AK34" t="inlineStr"/>
+      <c r="AL34" t="inlineStr"/>
+      <c r="AM34" t="inlineStr"/>
+      <c r="AN34" t="inlineStr"/>
+      <c r="AO34" t="inlineStr"/>
+      <c r="AP34" t="inlineStr"/>
+      <c r="AQ34" t="inlineStr"/>
+      <c r="AR34" t="inlineStr"/>
+      <c r="AS34" t="inlineStr"/>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AU34" t="inlineStr"/>
+      <c r="AV34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2016-11</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>100</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0</v>
+      </c>
+      <c r="D35" t="n">
+        <v>16.66666666666666</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" t="n">
+        <v>16.66666666666666</v>
+      </c>
+      <c r="G35" t="n">
+        <v>16.66666666666666</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="n">
+        <v>16.66666666666666</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" t="n">
+        <v>16.66666666666666</v>
+      </c>
+      <c r="N35" t="n">
+        <v>33.33333333333333</v>
+      </c>
+      <c r="O35" t="n">
+        <v>50</v>
+      </c>
+      <c r="P35" t="inlineStr"/>
+      <c r="Q35" t="inlineStr"/>
+      <c r="R35" t="inlineStr"/>
+      <c r="S35" t="inlineStr"/>
+      <c r="T35" t="inlineStr"/>
+      <c r="U35" t="inlineStr"/>
+      <c r="V35" t="inlineStr"/>
+      <c r="W35" t="inlineStr"/>
+      <c r="X35" t="inlineStr"/>
+      <c r="Y35" t="inlineStr"/>
+      <c r="Z35" t="inlineStr"/>
+      <c r="AA35" t="inlineStr"/>
+      <c r="AB35" t="inlineStr"/>
+      <c r="AC35" t="inlineStr"/>
+      <c r="AD35" t="inlineStr"/>
+      <c r="AE35" t="inlineStr"/>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="inlineStr"/>
+      <c r="AH35" t="inlineStr"/>
+      <c r="AI35" t="inlineStr"/>
+      <c r="AJ35" t="inlineStr"/>
+      <c r="AK35" t="inlineStr"/>
+      <c r="AL35" t="inlineStr"/>
+      <c r="AM35" t="inlineStr"/>
+      <c r="AN35" t="inlineStr"/>
+      <c r="AO35" t="inlineStr"/>
+      <c r="AP35" t="inlineStr"/>
+      <c r="AQ35" t="inlineStr"/>
+      <c r="AR35" t="inlineStr"/>
+      <c r="AS35" t="inlineStr"/>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AU35" t="inlineStr"/>
+      <c r="AV35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2016-12</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>100</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" t="n">
+        <v>50</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" t="n">
+        <v>50</v>
+      </c>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr"/>
+      <c r="R36" t="inlineStr"/>
+      <c r="S36" t="inlineStr"/>
+      <c r="T36" t="inlineStr"/>
+      <c r="U36" t="inlineStr"/>
+      <c r="V36" t="inlineStr"/>
+      <c r="W36" t="inlineStr"/>
+      <c r="X36" t="inlineStr"/>
+      <c r="Y36" t="inlineStr"/>
+      <c r="Z36" t="inlineStr"/>
+      <c r="AA36" t="inlineStr"/>
+      <c r="AB36" t="inlineStr"/>
+      <c r="AC36" t="inlineStr"/>
+      <c r="AD36" t="inlineStr"/>
+      <c r="AE36" t="inlineStr"/>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="inlineStr"/>
+      <c r="AH36" t="inlineStr"/>
+      <c r="AI36" t="inlineStr"/>
+      <c r="AJ36" t="inlineStr"/>
+      <c r="AK36" t="inlineStr"/>
+      <c r="AL36" t="inlineStr"/>
+      <c r="AM36" t="inlineStr"/>
+      <c r="AN36" t="inlineStr"/>
+      <c r="AO36" t="inlineStr"/>
+      <c r="AP36" t="inlineStr"/>
+      <c r="AQ36" t="inlineStr"/>
+      <c r="AR36" t="inlineStr"/>
+      <c r="AS36" t="inlineStr"/>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AU36" t="inlineStr"/>
+      <c r="AV36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2017-03</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>100</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0</v>
+      </c>
+      <c r="D37" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" t="n">
+        <v>33.33333333333333</v>
+      </c>
+      <c r="F37" t="n">
+        <v>33.33333333333333</v>
+      </c>
+      <c r="G37" t="n">
+        <v>33.33333333333333</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" t="n">
+        <v>33.33333333333333</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="inlineStr"/>
+      <c r="Q37" t="inlineStr"/>
+      <c r="R37" t="inlineStr"/>
+      <c r="S37" t="inlineStr"/>
+      <c r="T37" t="inlineStr"/>
+      <c r="U37" t="inlineStr"/>
+      <c r="V37" t="inlineStr"/>
+      <c r="W37" t="inlineStr"/>
+      <c r="X37" t="inlineStr"/>
+      <c r="Y37" t="inlineStr"/>
+      <c r="Z37" t="inlineStr"/>
+      <c r="AA37" t="inlineStr"/>
+      <c r="AB37" t="inlineStr"/>
+      <c r="AC37" t="inlineStr"/>
+      <c r="AD37" t="inlineStr"/>
+      <c r="AE37" t="inlineStr"/>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="inlineStr"/>
+      <c r="AH37" t="inlineStr"/>
+      <c r="AI37" t="inlineStr"/>
+      <c r="AJ37" t="inlineStr"/>
+      <c r="AK37" t="inlineStr"/>
+      <c r="AL37" t="inlineStr"/>
+      <c r="AM37" t="inlineStr"/>
+      <c r="AN37" t="inlineStr"/>
+      <c r="AO37" t="inlineStr"/>
+      <c r="AP37" t="inlineStr"/>
+      <c r="AQ37" t="inlineStr"/>
+      <c r="AR37" t="inlineStr"/>
+      <c r="AS37" t="inlineStr"/>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AU37" t="inlineStr"/>
+      <c r="AV37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2017-04</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>100</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" t="inlineStr"/>
+      <c r="Q38" t="inlineStr"/>
+      <c r="R38" t="inlineStr"/>
+      <c r="S38" t="inlineStr"/>
+      <c r="T38" t="inlineStr"/>
+      <c r="U38" t="inlineStr"/>
+      <c r="V38" t="inlineStr"/>
+      <c r="W38" t="inlineStr"/>
+      <c r="X38" t="inlineStr"/>
+      <c r="Y38" t="inlineStr"/>
+      <c r="Z38" t="inlineStr"/>
+      <c r="AA38" t="inlineStr"/>
+      <c r="AB38" t="inlineStr"/>
+      <c r="AC38" t="inlineStr"/>
+      <c r="AD38" t="inlineStr"/>
+      <c r="AE38" t="inlineStr"/>
+      <c r="AF38" t="inlineStr"/>
+      <c r="AG38" t="inlineStr"/>
+      <c r="AH38" t="inlineStr"/>
+      <c r="AI38" t="inlineStr"/>
+      <c r="AJ38" t="inlineStr"/>
+      <c r="AK38" t="inlineStr"/>
+      <c r="AL38" t="inlineStr"/>
+      <c r="AM38" t="inlineStr"/>
+      <c r="AN38" t="inlineStr"/>
+      <c r="AO38" t="inlineStr"/>
+      <c r="AP38" t="inlineStr"/>
+      <c r="AQ38" t="inlineStr"/>
+      <c r="AR38" t="inlineStr"/>
+      <c r="AS38" t="inlineStr"/>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AU38" t="inlineStr"/>
+      <c r="AV38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2017-06</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>100</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0</v>
+      </c>
+      <c r="D39" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" t="n">
+        <v>100</v>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr"/>
+      <c r="P39" t="inlineStr"/>
+      <c r="Q39" t="inlineStr"/>
+      <c r="R39" t="inlineStr"/>
+      <c r="S39" t="inlineStr"/>
+      <c r="T39" t="inlineStr"/>
+      <c r="U39" t="inlineStr"/>
+      <c r="V39" t="inlineStr"/>
+      <c r="W39" t="inlineStr"/>
+      <c r="X39" t="inlineStr"/>
+      <c r="Y39" t="inlineStr"/>
+      <c r="Z39" t="inlineStr"/>
+      <c r="AA39" t="inlineStr"/>
+      <c r="AB39" t="inlineStr"/>
+      <c r="AC39" t="inlineStr"/>
+      <c r="AD39" t="inlineStr"/>
+      <c r="AE39" t="inlineStr"/>
+      <c r="AF39" t="inlineStr"/>
+      <c r="AG39" t="inlineStr"/>
+      <c r="AH39" t="inlineStr"/>
+      <c r="AI39" t="inlineStr"/>
+      <c r="AJ39" t="inlineStr"/>
+      <c r="AK39" t="inlineStr"/>
+      <c r="AL39" t="inlineStr"/>
+      <c r="AM39" t="inlineStr"/>
+      <c r="AN39" t="inlineStr"/>
+      <c r="AO39" t="inlineStr"/>
+      <c r="AP39" t="inlineStr"/>
+      <c r="AQ39" t="inlineStr"/>
+      <c r="AR39" t="inlineStr"/>
+      <c r="AS39" t="inlineStr"/>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AU39" t="inlineStr"/>
+      <c r="AV39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2017-07</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>100</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0</v>
+      </c>
+      <c r="D40" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" t="n">
+        <v>50</v>
+      </c>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr"/>
+      <c r="P40" t="inlineStr"/>
+      <c r="Q40" t="inlineStr"/>
+      <c r="R40" t="inlineStr"/>
+      <c r="S40" t="inlineStr"/>
+      <c r="T40" t="inlineStr"/>
+      <c r="U40" t="inlineStr"/>
+      <c r="V40" t="inlineStr"/>
+      <c r="W40" t="inlineStr"/>
+      <c r="X40" t="inlineStr"/>
+      <c r="Y40" t="inlineStr"/>
+      <c r="Z40" t="inlineStr"/>
+      <c r="AA40" t="inlineStr"/>
+      <c r="AB40" t="inlineStr"/>
+      <c r="AC40" t="inlineStr"/>
+      <c r="AD40" t="inlineStr"/>
+      <c r="AE40" t="inlineStr"/>
+      <c r="AF40" t="inlineStr"/>
+      <c r="AG40" t="inlineStr"/>
+      <c r="AH40" t="inlineStr"/>
+      <c r="AI40" t="inlineStr"/>
+      <c r="AJ40" t="inlineStr"/>
+      <c r="AK40" t="inlineStr"/>
+      <c r="AL40" t="inlineStr"/>
+      <c r="AM40" t="inlineStr"/>
+      <c r="AN40" t="inlineStr"/>
+      <c r="AO40" t="inlineStr"/>
+      <c r="AP40" t="inlineStr"/>
+      <c r="AQ40" t="inlineStr"/>
+      <c r="AR40" t="inlineStr"/>
+      <c r="AS40" t="inlineStr"/>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AU40" t="inlineStr"/>
+      <c r="AV40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2017-09</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>100</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0</v>
+      </c>
+      <c r="D41" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr"/>
+      <c r="P41" t="inlineStr"/>
+      <c r="Q41" t="inlineStr"/>
+      <c r="R41" t="inlineStr"/>
+      <c r="S41" t="inlineStr"/>
+      <c r="T41" t="inlineStr"/>
+      <c r="U41" t="inlineStr"/>
+      <c r="V41" t="inlineStr"/>
+      <c r="W41" t="inlineStr"/>
+      <c r="X41" t="inlineStr"/>
+      <c r="Y41" t="inlineStr"/>
+      <c r="Z41" t="inlineStr"/>
+      <c r="AA41" t="inlineStr"/>
+      <c r="AB41" t="inlineStr"/>
+      <c r="AC41" t="inlineStr"/>
+      <c r="AD41" t="inlineStr"/>
+      <c r="AE41" t="inlineStr"/>
+      <c r="AF41" t="inlineStr"/>
+      <c r="AG41" t="inlineStr"/>
+      <c r="AH41" t="inlineStr"/>
+      <c r="AI41" t="inlineStr"/>
+      <c r="AJ41" t="inlineStr"/>
+      <c r="AK41" t="inlineStr"/>
+      <c r="AL41" t="inlineStr"/>
+      <c r="AM41" t="inlineStr"/>
+      <c r="AN41" t="inlineStr"/>
+      <c r="AO41" t="inlineStr"/>
+      <c r="AP41" t="inlineStr"/>
+      <c r="AQ41" t="inlineStr"/>
+      <c r="AR41" t="inlineStr"/>
+      <c r="AS41" t="inlineStr"/>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AU41" t="inlineStr"/>
+      <c r="AV41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2017-10</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>100</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0</v>
+      </c>
+      <c r="D42" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" t="inlineStr"/>
+      <c r="P42" t="inlineStr"/>
+      <c r="Q42" t="inlineStr"/>
+      <c r="R42" t="inlineStr"/>
+      <c r="S42" t="inlineStr"/>
+      <c r="T42" t="inlineStr"/>
+      <c r="U42" t="inlineStr"/>
+      <c r="V42" t="inlineStr"/>
+      <c r="W42" t="inlineStr"/>
+      <c r="X42" t="inlineStr"/>
+      <c r="Y42" t="inlineStr"/>
+      <c r="Z42" t="inlineStr"/>
+      <c r="AA42" t="inlineStr"/>
+      <c r="AB42" t="inlineStr"/>
+      <c r="AC42" t="inlineStr"/>
+      <c r="AD42" t="inlineStr"/>
+      <c r="AE42" t="inlineStr"/>
+      <c r="AF42" t="inlineStr"/>
+      <c r="AG42" t="inlineStr"/>
+      <c r="AH42" t="inlineStr"/>
+      <c r="AI42" t="inlineStr"/>
+      <c r="AJ42" t="inlineStr"/>
+      <c r="AK42" t="inlineStr"/>
+      <c r="AL42" t="inlineStr"/>
+      <c r="AM42" t="inlineStr"/>
+      <c r="AN42" t="inlineStr"/>
+      <c r="AO42" t="inlineStr"/>
+      <c r="AP42" t="inlineStr"/>
+      <c r="AQ42" t="inlineStr"/>
+      <c r="AR42" t="inlineStr"/>
+      <c r="AS42" t="inlineStr"/>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AU42" t="inlineStr"/>
+      <c r="AV42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2017-11</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>100</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0</v>
+      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" t="inlineStr"/>
+      <c r="P43" t="inlineStr"/>
+      <c r="Q43" t="inlineStr"/>
+      <c r="R43" t="inlineStr"/>
+      <c r="S43" t="inlineStr"/>
+      <c r="T43" t="inlineStr"/>
+      <c r="U43" t="inlineStr"/>
+      <c r="V43" t="inlineStr"/>
+      <c r="W43" t="inlineStr"/>
+      <c r="X43" t="inlineStr"/>
+      <c r="Y43" t="inlineStr"/>
+      <c r="Z43" t="inlineStr"/>
+      <c r="AA43" t="inlineStr"/>
+      <c r="AB43" t="inlineStr"/>
+      <c r="AC43" t="inlineStr"/>
+      <c r="AD43" t="inlineStr"/>
+      <c r="AE43" t="inlineStr"/>
+      <c r="AF43" t="inlineStr"/>
+      <c r="AG43" t="inlineStr"/>
+      <c r="AH43" t="inlineStr"/>
+      <c r="AI43" t="inlineStr"/>
+      <c r="AJ43" t="inlineStr"/>
+      <c r="AK43" t="inlineStr"/>
+      <c r="AL43" t="inlineStr"/>
+      <c r="AM43" t="inlineStr"/>
+      <c r="AN43" t="inlineStr"/>
+      <c r="AO43" t="inlineStr"/>
+      <c r="AP43" t="inlineStr"/>
+      <c r="AQ43" t="inlineStr"/>
+      <c r="AR43" t="inlineStr"/>
+      <c r="AS43" t="inlineStr"/>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AU43" t="inlineStr"/>
+      <c r="AV43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D43"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>cohort_month</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>sales</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>profit</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>customers</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2014-01</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>105234.2638</v>
+      </c>
+      <c r="C2" t="n">
+        <v>20859.3737</v>
+      </c>
+      <c r="D2" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2014-02</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>78497.29550000001</v>
+      </c>
+      <c r="C3" t="n">
+        <v>13515.7394</v>
+      </c>
+      <c r="D3" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2014-03</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>221986.4116</v>
+      </c>
+      <c r="C4" t="n">
+        <v>14450.7607</v>
+      </c>
+      <c r="D4" t="n">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2014-04</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>183881.4128</v>
+      </c>
+      <c r="C5" t="n">
+        <v>25680.1816</v>
+      </c>
+      <c r="D5" t="n">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2014-05</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>174869.0172</v>
+      </c>
+      <c r="C6" t="n">
+        <v>16503.4947</v>
+      </c>
+      <c r="D6" t="n">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2014-06</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>146464.462</v>
+      </c>
+      <c r="C7" t="n">
+        <v>7723.7447</v>
+      </c>
+      <c r="D7" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2014-07</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>135636.7698</v>
+      </c>
+      <c r="C8" t="n">
+        <v>12260.2378</v>
+      </c>
+      <c r="D8" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2014-08</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>137859.2135</v>
+      </c>
+      <c r="C9" t="n">
+        <v>20564.2105</v>
+      </c>
+      <c r="D9" t="n">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2014-09</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>208099.8588</v>
+      </c>
+      <c r="C10" t="n">
+        <v>20877.3515</v>
+      </c>
+      <c r="D10" t="n">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2014-10</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>123625.3107</v>
+      </c>
+      <c r="C11" t="n">
+        <v>12146.8607</v>
+      </c>
+      <c r="D11" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2014-11</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>201083.5169</v>
+      </c>
+      <c r="C12" t="n">
+        <v>37505.0764</v>
+      </c>
+      <c r="D12" t="n">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2014-12</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>119805.706</v>
+      </c>
+      <c r="C13" t="n">
+        <v>17723.611</v>
+      </c>
+      <c r="D13" t="n">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2015-01</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>18382.719</v>
+      </c>
+      <c r="C14" t="n">
+        <v>2707.9043</v>
+      </c>
+      <c r="D14" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2015-02</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>20132.345</v>
+      </c>
+      <c r="C15" t="n">
+        <v>2742.1423</v>
+      </c>
+      <c r="D15" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2015-03</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>50685.9466</v>
+      </c>
+      <c r="C16" t="n">
+        <v>10310.0693</v>
+      </c>
+      <c r="D16" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2015-04</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>35742.848</v>
+      </c>
+      <c r="C17" t="n">
+        <v>4120.1653</v>
+      </c>
+      <c r="D17" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2015-05</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>27876.6216</v>
+      </c>
+      <c r="C18" t="n">
+        <v>-943.5886000000002</v>
+      </c>
+      <c r="D18" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2015-06</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>38162.175</v>
+      </c>
+      <c r="C19" t="n">
+        <v>4609.9087</v>
+      </c>
+      <c r="D19" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2015-07</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>12860.987</v>
+      </c>
+      <c r="C20" t="n">
+        <v>2176.2017</v>
+      </c>
+      <c r="D20" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2015-08</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>25369.421</v>
+      </c>
+      <c r="C21" t="n">
+        <v>5878.3959</v>
+      </c>
+      <c r="D21" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2015-09</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>46844.184</v>
+      </c>
+      <c r="C22" t="n">
+        <v>9286.4187</v>
+      </c>
+      <c r="D22" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2015-10</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>14550.2895</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1467.1776</v>
+      </c>
+      <c r="D23" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2015-11</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>19565.6656</v>
+      </c>
+      <c r="C24" t="n">
+        <v>1384.492</v>
+      </c>
+      <c r="D24" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2015-12</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>26481.364</v>
+      </c>
+      <c r="C25" t="n">
+        <v>2653.7024</v>
+      </c>
+      <c r="D25" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2016-01</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>10892.6378</v>
+      </c>
+      <c r="C26" t="n">
+        <v>2599.5637</v>
+      </c>
+      <c r="D26" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2016-02</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>2605.518</v>
+      </c>
+      <c r="C27" t="n">
+        <v>825.5822999999999</v>
+      </c>
+      <c r="D27" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2016-03</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>20013.153</v>
+      </c>
+      <c r="C28" t="n">
+        <v>1000.1308</v>
+      </c>
+      <c r="D28" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2016-04</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>21595.595</v>
+      </c>
+      <c r="C29" t="n">
+        <v>7592.4691</v>
+      </c>
+      <c r="D29" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2016-05</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>27788.3286</v>
+      </c>
+      <c r="C30" t="n">
+        <v>4128.8088</v>
+      </c>
+      <c r="D30" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2016-06</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>13977.545</v>
+      </c>
+      <c r="C31" t="n">
+        <v>1288.1042</v>
+      </c>
+      <c r="D31" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2016-07</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>138.338</v>
+      </c>
+      <c r="C32" t="n">
+        <v>51.2837</v>
+      </c>
+      <c r="D32" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2016-08</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>8397.259</v>
+      </c>
+      <c r="C33" t="n">
+        <v>587.4447</v>
+      </c>
+      <c r="D33" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2016-10</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>2533.314</v>
+      </c>
+      <c r="C34" t="n">
+        <v>-394.3686</v>
+      </c>
+      <c r="D34" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2016-11</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>5054.422</v>
+      </c>
+      <c r="C35" t="n">
+        <v>-71.0376</v>
+      </c>
+      <c r="D35" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2016-12</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>2713.768</v>
+      </c>
+      <c r="C36" t="n">
+        <v>791.2996000000001</v>
+      </c>
+      <c r="D36" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2017-03</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>1935.11</v>
+      </c>
+      <c r="C37" t="n">
+        <v>459.9251</v>
+      </c>
+      <c r="D37" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2017-04</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>16.739</v>
+      </c>
+      <c r="C38" t="n">
+        <v>-1.2453</v>
+      </c>
+      <c r="D38" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2017-06</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>113.832</v>
+      </c>
+      <c r="C39" t="n">
+        <v>33.8706</v>
+      </c>
+      <c r="D39" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2017-07</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>1608.752</v>
+      </c>
+      <c r="C40" t="n">
+        <v>659.1837</v>
+      </c>
+      <c r="D40" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2017-09</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>1038.26</v>
+      </c>
+      <c r="C41" t="n">
+        <v>265.5332</v>
+      </c>
+      <c r="D41" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2017-10</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>1593.528</v>
+      </c>
+      <c r="C42" t="n">
+        <v>155.8728</v>
+      </c>
+      <c r="D42" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2017-11</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>1205.584</v>
+      </c>
+      <c r="C43" t="n">
+        <v>233.0274</v>
+      </c>
+      <c r="D43" t="n">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>cohort_year</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>customers</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>sales</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>profit</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>sales_share_pct</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>2014</v>
+      </c>
+      <c r="B2" t="n">
+        <v>595</v>
+      </c>
+      <c r="C2" t="n">
+        <v>1837043.2386</v>
+      </c>
+      <c r="D2" t="n">
+        <v>219810.6427</v>
+      </c>
+      <c r="E2" t="n">
+        <v>79.97856468010708</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2015</v>
+      </c>
+      <c r="B3" t="n">
+        <v>136</v>
+      </c>
+      <c r="C3" t="n">
+        <v>336654.5663</v>
+      </c>
+      <c r="D3" t="n">
+        <v>46392.9896</v>
+      </c>
+      <c r="E3" t="n">
+        <v>14.65678566509814</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2016</v>
+      </c>
+      <c r="B4" t="n">
+        <v>51</v>
+      </c>
+      <c r="C4" t="n">
+        <v>115709.8784</v>
+      </c>
+      <c r="D4" t="n">
+        <v>18399.2807</v>
+      </c>
+      <c r="E4" t="n">
+        <v>5.037611417788066</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>2017</v>
+      </c>
+      <c r="B5" t="n">
+        <v>11</v>
+      </c>
+      <c r="C5" t="n">
+        <v>7511.805</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1806.1675</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.3270382370067159</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>year</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>returning_sales</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>new_customer_sales</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>new_customer_share_pct</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>2014</v>
+      </c>
+      <c r="B2" t="n">
+        <v>173243.4331</v>
+      </c>
+      <c r="C2" t="n">
+        <v>310722.693</v>
+      </c>
+      <c r="D2" t="n">
+        <v>64.20339694100753</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2015</v>
+      </c>
+      <c r="B3" t="n">
+        <v>408229.8283</v>
+      </c>
+      <c r="C3" t="n">
+        <v>62302.6807</v>
+      </c>
+      <c r="D3" t="n">
+        <v>13.24088761314471</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2016</v>
+      </c>
+      <c r="B4" t="n">
+        <v>582278.267</v>
+      </c>
+      <c r="C4" t="n">
+        <v>26927.331</v>
+      </c>
+      <c r="D4" t="n">
+        <v>4.420072810952732</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>2017</v>
+      </c>
+      <c r="B5" t="n">
+        <v>727458.0502000001</v>
+      </c>
+      <c r="C5" t="n">
+        <v>5757.205</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.7851998385425847</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>discount_band</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>lines</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>sales</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>profit</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>avg_line_sales</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>avg_units_per_line</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>pct_lines_losing</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>margin_pct</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>4798</v>
+      </c>
+      <c r="C2" t="n">
+        <v>1087908.47</v>
+      </c>
+      <c r="D2" t="n">
+        <v>320987.6032</v>
+      </c>
+      <c r="E2" t="n">
+        <v>226.742073780742</v>
+      </c>
+      <c r="F2" t="n">
+        <v>3.807211338057524</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>29.50501922280282</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>1-10%</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>94</v>
+      </c>
+      <c r="C3" t="n">
+        <v>54369.351</v>
+      </c>
+      <c r="D3" t="n">
+        <v>9029.177</v>
+      </c>
+      <c r="E3" t="n">
+        <v>578.3973510638298</v>
+      </c>
+      <c r="F3" t="n">
+        <v>3.968085106382979</v>
+      </c>
+      <c r="G3" t="n">
+        <v>4.25531914893617</v>
+      </c>
+      <c r="H3" t="n">
+        <v>16.60710829525995</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>11-20%</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>3709</v>
+      </c>
+      <c r="C4" t="n">
+        <v>792152.8895</v>
+      </c>
+      <c r="D4" t="n">
+        <v>91756.2975</v>
+      </c>
+      <c r="E4" t="n">
+        <v>213.5758666756538</v>
+      </c>
+      <c r="F4" t="n">
+        <v>3.736317066594769</v>
+      </c>
+      <c r="G4" t="n">
+        <v>13.9929900242653</v>
+      </c>
+      <c r="H4" t="n">
+        <v>11.58315505961428</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>21-30%</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>226</v>
+      </c>
+      <c r="C5" t="n">
+        <v>102945.283</v>
+      </c>
+      <c r="D5" t="n">
+        <v>-10357.2186</v>
+      </c>
+      <c r="E5" t="n">
+        <v>455.5101017699115</v>
+      </c>
+      <c r="F5" t="n">
+        <v>3.747787610619469</v>
+      </c>
+      <c r="G5" t="n">
+        <v>91.59292035398229</v>
+      </c>
+      <c r="H5" t="n">
+        <v>-10.0608967192795</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>31-40%</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>233</v>
+      </c>
+      <c r="C6" t="n">
+        <v>130911.2428</v>
+      </c>
+      <c r="D6" t="n">
+        <v>-25448.1881</v>
+      </c>
+      <c r="E6" t="n">
+        <v>561.8508274678112</v>
+      </c>
+      <c r="F6" t="n">
+        <v>3.824034334763949</v>
+      </c>
+      <c r="G6" t="n">
+        <v>88.8412017167382</v>
+      </c>
+      <c r="H6" t="n">
+        <v>-19.43926858816743</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>41-50%</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>77</v>
+      </c>
+      <c r="C7" t="n">
+        <v>64403.514</v>
+      </c>
+      <c r="D7" t="n">
+        <v>-22999.5392</v>
+      </c>
+      <c r="E7" t="n">
+        <v>836.4092727272728</v>
+      </c>
+      <c r="F7" t="n">
+        <v>3.714285714285714</v>
+      </c>
+      <c r="G7" t="n">
+        <v>100</v>
+      </c>
+      <c r="H7" t="n">
+        <v>-35.71162157394082</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>51-80%</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>856</v>
+      </c>
+      <c r="C8" t="n">
+        <v>64228.738</v>
+      </c>
+      <c r="D8" t="n">
+        <v>-76559.05130000001</v>
+      </c>
+      <c r="E8" t="n">
+        <v>75.03357242990654</v>
+      </c>
+      <c r="F8" t="n">
+        <v>3.912383177570093</v>
+      </c>
+      <c r="G8" t="n">
+        <v>100</v>
+      </c>
+      <c r="H8" t="n">
+        <v>-119.1975020589693</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>sub_category</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>avg_discount</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>lines</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>profit</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>pct_lines_over_20</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Binders</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0.3722915298752462</v>
+      </c>
+      <c r="C2" t="n">
+        <v>1523</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30221.7633</v>
+      </c>
+      <c r="E2" t="n">
+        <v>40.24950755088641</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Machines</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0.3060869565217391</v>
+      </c>
+      <c r="C3" t="n">
+        <v>115</v>
+      </c>
+      <c r="D3" t="n">
+        <v>3384.7569</v>
+      </c>
+      <c r="E3" t="n">
+        <v>46.08695652173913</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Tables</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0.2612852664576803</v>
+      </c>
+      <c r="C4" t="n">
+        <v>319</v>
+      </c>
+      <c r="D4" t="n">
+        <v>-17725.4811</v>
+      </c>
+      <c r="E4" t="n">
+        <v>55.17241379310344</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Bookcases</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0.211140350877193</v>
+      </c>
+      <c r="C5" t="n">
+        <v>228</v>
+      </c>
+      <c r="D5" t="n">
+        <v>-3472.556</v>
+      </c>
+      <c r="E5" t="n">
+        <v>30.70175438596491</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Chairs</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.1699675324675325</v>
+      </c>
+      <c r="C6" t="n">
+        <v>616</v>
+      </c>
+      <c r="D6" t="n">
+        <v>26602.2251</v>
+      </c>
+      <c r="E6" t="n">
+        <v>25.48701298701299</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Appliances</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.1665236051502146</v>
+      </c>
+      <c r="C7" t="n">
+        <v>466</v>
+      </c>
+      <c r="D7" t="n">
+        <v>18138.0054</v>
+      </c>
+      <c r="E7" t="n">
+        <v>14.37768240343348</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Copiers</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0.1617647058823529</v>
+      </c>
+      <c r="C8" t="n">
+        <v>68</v>
+      </c>
+      <c r="D8" t="n">
+        <v>55617.8249</v>
+      </c>
+      <c r="E8" t="n">
+        <v>13.23529411764706</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Phones</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.1545556805399325</v>
+      </c>
+      <c r="C9" t="n">
+        <v>889</v>
+      </c>
+      <c r="D9" t="n">
+        <v>44515.7306</v>
+      </c>
+      <c r="E9" t="n">
+        <v>12.26096737907762</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Furnishings</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.1383490073145246</v>
+      </c>
+      <c r="C10" t="n">
+        <v>957</v>
+      </c>
+      <c r="D10" t="n">
+        <v>13059.1436</v>
+      </c>
+      <c r="E10" t="n">
+        <v>14.42006269592476</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Fasteners</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0.08202764976958525</v>
+      </c>
+      <c r="C11" t="n">
+        <v>217</v>
+      </c>
+      <c r="D11" t="n">
+        <v>949.5182</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Envelopes</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0.08031496062992127</v>
+      </c>
+      <c r="C12" t="n">
+        <v>254</v>
+      </c>
+      <c r="D12" t="n">
+        <v>6964.1767</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Accessories</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>0.07845161290322582</v>
+      </c>
+      <c r="C13" t="n">
+        <v>775</v>
+      </c>
+      <c r="D13" t="n">
+        <v>41936.6357</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Supplies</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>0.07684210526315791</v>
+      </c>
+      <c r="C14" t="n">
+        <v>190</v>
+      </c>
+      <c r="D14" t="n">
+        <v>-1189.0995</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>0.07489051094890511</v>
+      </c>
+      <c r="C15" t="n">
+        <v>1370</v>
+      </c>
+      <c r="D15" t="n">
+        <v>34053.5693</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Art</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>0.07487437185929649</v>
+      </c>
+      <c r="C16" t="n">
+        <v>796</v>
+      </c>
+      <c r="D16" t="n">
+        <v>6527.787</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Storage</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>0.07470449172576832</v>
+      </c>
+      <c r="C17" t="n">
+        <v>846</v>
+      </c>
+      <c r="D17" t="n">
+        <v>21278.8264</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Labels</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>0.06868131868131869</v>
+      </c>
+      <c r="C18" t="n">
+        <v>364</v>
+      </c>
+      <c r="D18" t="n">
+        <v>5546.254</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>category</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>avg_discount</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>lines</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>pct_lines_over_20</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>profit_lines_over_20</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>profit_lines_up_to_20</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Furniture</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0.1738632075471698</v>
+      </c>
+      <c r="C2" t="n">
+        <v>2120</v>
+      </c>
+      <c r="D2" t="n">
+        <v>25.5188679245283</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-54465.6973</v>
+      </c>
+      <c r="F2" t="n">
+        <v>72929.0289</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Office Supplies</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0.1572850979090608</v>
+      </c>
+      <c r="C3" t="n">
+        <v>6026</v>
+      </c>
+      <c r="D3" t="n">
+        <v>11.28443411881845</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-47140.1376</v>
+      </c>
+      <c r="F3" t="n">
+        <v>169630.9384</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0.1323226854358419</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1847</v>
+      </c>
+      <c r="D4" t="n">
+        <v>9.258256632376828</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-33758.1623</v>
+      </c>
+      <c r="F4" t="n">
+        <v>179213.1104</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -24326,6 +30693,274 @@
       </c>
       <c r="F5" t="n">
         <v>12.74377052813944</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>avg_discount</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>pct_lines_over_20</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>profit_lines_over_20</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Central</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0.2403529918209212</v>
+      </c>
+      <c r="C2" t="n">
+        <v>27.67972449418855</v>
+      </c>
+      <c r="D2" t="n">
+        <v>-52392.2744</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>East</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0.1453108535300316</v>
+      </c>
+      <c r="C3" t="n">
+        <v>16.15735862311205</v>
+      </c>
+      <c r="D3" t="n">
+        <v>-42076.5488</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0.1472530864197531</v>
+      </c>
+      <c r="C4" t="n">
+        <v>10.55555555555556</v>
+      </c>
+      <c r="D4" t="n">
+        <v>-24880.4818</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>West</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0.1093349984389635</v>
+      </c>
+      <c r="C5" t="n">
+        <v>3.684046206681237</v>
+      </c>
+      <c r="D5" t="n">
+        <v>-16014.6922</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>quadrant</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>products</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>sales</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>profit</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>loss_making</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>products_pct</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>sales_share_pct</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>profit_share_pct</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>High sales / High profit</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>673</v>
+      </c>
+      <c r="C2" t="n">
+        <v>1573502.1204</v>
+      </c>
+      <c r="D2" t="n">
+        <v>332719.4441</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>36.37837837837838</v>
+      </c>
+      <c r="G2" t="n">
+        <v>68.50488789071937</v>
+      </c>
+      <c r="H2" t="n">
+        <v>116.169307034244</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>High sales / Low profit</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>252</v>
+      </c>
+      <c r="C3" t="n">
+        <v>613464.4929</v>
+      </c>
+      <c r="D3" t="n">
+        <v>-72632.4393</v>
+      </c>
+      <c r="E3" t="n">
+        <v>198</v>
+      </c>
+      <c r="F3" t="n">
+        <v>13.62162162162162</v>
+      </c>
+      <c r="G3" t="n">
+        <v>26.70814088281511</v>
+      </c>
+      <c r="H3" t="n">
+        <v>-25.35968453695727</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Low sales / High profit</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>252</v>
+      </c>
+      <c r="C4" t="n">
+        <v>48950.092</v>
+      </c>
+      <c r="D4" t="n">
+        <v>17720.6736</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>13.62162162162162</v>
+      </c>
+      <c r="G4" t="n">
+        <v>2.131119190260736</v>
+      </c>
+      <c r="H4" t="n">
+        <v>6.187189864603471</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Low sales / Low profit</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>673</v>
+      </c>
+      <c r="C5" t="n">
+        <v>61002.783</v>
+      </c>
+      <c r="D5" t="n">
+        <v>8601.402099999999</v>
+      </c>
+      <c r="E5" t="n">
+        <v>103</v>
+      </c>
+      <c r="F5" t="n">
+        <v>36.37837837837838</v>
+      </c>
+      <c r="G5" t="n">
+        <v>2.655852036204782</v>
+      </c>
+      <c r="H5" t="n">
+        <v>3.003187638109818</v>
       </c>
     </row>
   </sheetData>
